--- a/時間帯別稼働推移-結果.xlsx
+++ b/時間帯別稼働推移-結果.xlsx
@@ -227,7 +227,7 @@
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -19148,76 +19148,76 @@
         <v>0</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>6.8</v>
+        <v>5.97</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>7.1</v>
+        <v>6.13</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>7</v>
+        <v>6.17</v>
       </c>
       <c r="H2" s="9" t="n">
-        <v>7</v>
+        <v>5.92</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>6.7</v>
+        <v>5.29</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>6.45</v>
+        <v>5.36</v>
       </c>
       <c r="L2" s="9" t="n">
-        <v>7.6</v>
+        <v>6.38</v>
       </c>
       <c r="M2" s="9" t="n">
-        <v>7.55</v>
+        <v>6.6</v>
       </c>
       <c r="N2" s="9" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="O2" s="9" t="n">
-        <v>7.45</v>
+        <v>6.38</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>7.35</v>
+        <v>6.25</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>7.1</v>
+        <v>5.84</v>
       </c>
       <c r="R2" s="9" t="n">
-        <v>6.6</v>
+        <v>5.59</v>
       </c>
       <c r="S2" s="9" t="n">
-        <v>6.15</v>
+        <v>4.93</v>
       </c>
       <c r="T2" s="9" t="n">
-        <v>5.25</v>
+        <v>3.96</v>
       </c>
       <c r="U2" s="9" t="n">
-        <v>4.05</v>
+        <v>3.13</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="W2" s="9" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="X2" s="9" t="n">
-        <v>1.7</v>
+        <v>1.13</v>
       </c>
       <c r="Y2" s="9" t="n">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="Z2" s="9" t="n">
-        <v>0.8</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="3">
@@ -19230,76 +19230,76 @@
         <v>0</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>6.3</v>
+        <v>5.56</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>6.4</v>
+        <v>6.05</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>6.5</v>
+        <v>5.59</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>6.3</v>
+        <v>5.49</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>6.2</v>
+        <v>5.24</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>6.2</v>
+        <v>5.15</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>5.95</v>
+        <v>4.68</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>5.65</v>
+        <v>4.71</v>
       </c>
       <c r="L3" s="9" t="n">
-        <v>6.65</v>
+        <v>5.5</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>6.5</v>
+        <v>5.57</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>6.55</v>
+        <v>5.4</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>6.15</v>
+        <v>5.15</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>5.95</v>
+        <v>5.12</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>5.75</v>
+        <v>4.73</v>
       </c>
       <c r="R3" s="9" t="n">
-        <v>5.05</v>
+        <v>4.33</v>
       </c>
       <c r="S3" s="9" t="n">
-        <v>4.55</v>
+        <v>3.67</v>
       </c>
       <c r="T3" s="9" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="U3" s="9" t="n">
-        <v>2.7</v>
+        <v>2.03</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>1.95</v>
+        <v>1.28</v>
       </c>
       <c r="W3" s="9" t="n">
-        <v>1.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="X3" s="9" t="n">
-        <v>0.85</v>
+        <v>0.52</v>
       </c>
       <c r="Y3" s="9" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
       <c r="Z3" s="9" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="5">
@@ -19401,76 +19401,76 @@
         <v>0</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>7.25</v>
+        <v>6.53</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>7.5</v>
+        <v>7.17</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>7.5</v>
+        <v>6.73</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>7.5</v>
+        <v>6.63</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>7.75</v>
+        <v>6.88</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>7.75</v>
+        <v>6.99</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>7</v>
+        <v>5.98</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>7</v>
+        <v>5.21</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>7</v>
+        <v>5.88</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>7.5</v>
+        <v>6.62</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>7.5</v>
+        <v>6.81</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>7.5</v>
+        <v>6.27</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>6.5</v>
+        <v>5.63</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>6.5</v>
+        <v>4.88</v>
       </c>
       <c r="R7" s="9" t="n">
-        <v>5.5</v>
+        <v>4.69</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>5.25</v>
+        <v>3.87</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>4.25</v>
+        <v>3.88</v>
       </c>
       <c r="U7" s="9" t="n">
-        <v>4.75</v>
+        <v>3.06</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="X7" s="9" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>1.25</v>
+        <v>0.73</v>
       </c>
       <c r="Z7" s="9" t="n">
-        <v>0.75</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="8">
@@ -19483,76 +19483,76 @@
         <v>0</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>6.25</v>
+        <v>5.74</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>6.5</v>
+        <v>6.17</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>6.5</v>
+        <v>5.68</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>6</v>
+        <v>5.18</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>6.25</v>
+        <v>5.47</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>6.25</v>
+        <v>5.74</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>5.75</v>
+        <v>4.73</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>5.75</v>
+        <v>4.29</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>6</v>
+        <v>4.87</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>5.75</v>
+        <v>5.07</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>5.5</v>
+        <v>5.17</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>5.75</v>
+        <v>4.77</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>5</v>
+        <v>4.51</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>5</v>
+        <v>3.74</v>
       </c>
       <c r="R8" s="9" t="n">
-        <v>4</v>
+        <v>3.51</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="T8" s="9" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U8" s="9" t="n">
-        <v>2.5</v>
+        <v>1.39</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>1</v>
       </c>
       <c r="X8" s="9" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="Z8" s="9" t="n">
-        <v>0.75</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="10">
@@ -19654,76 +19654,76 @@
         <v>0</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>7.75</v>
+        <v>6.83</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>7.75</v>
+        <v>6.42</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>7.75</v>
+        <v>6.72</v>
       </c>
       <c r="H12" s="9" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="N12" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="I12" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="L12" s="9" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="M12" s="9" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="N12" s="9" t="n">
-        <v>8.5</v>
-      </c>
       <c r="O12" s="9" t="n">
-        <v>8</v>
+        <v>7.12</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>7.75</v>
+        <v>6.58</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>7.75</v>
+        <v>6.67</v>
       </c>
       <c r="R12" s="9" t="n">
-        <v>7.5</v>
+        <v>6.62</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>6.5</v>
+        <v>5.14</v>
       </c>
       <c r="T12" s="9" t="n">
-        <v>5</v>
+        <v>3.33</v>
       </c>
       <c r="U12" s="9" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="X12" s="9" t="n">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>0.75</v>
       </c>
       <c r="Z12" s="9" t="n">
-        <v>0.75</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="13">
@@ -19736,76 +19736,76 @@
         <v>0</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>7.5</v>
+        <v>6.57</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>7.5</v>
+        <v>6.58</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>7.5</v>
+        <v>6.17</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>7.5</v>
+        <v>6.31</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>7</v>
+        <v>5.88</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>6.5</v>
+        <v>4.62</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>7.75</v>
+        <v>6.17</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>7.75</v>
+        <v>6.4</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>7.75</v>
+        <v>6.59</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>7.25</v>
+        <v>6.12</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>6.75</v>
+        <v>5.6</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>6.75</v>
+        <v>5.71</v>
       </c>
       <c r="R13" s="9" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>5</v>
+        <v>4.06</v>
       </c>
       <c r="T13" s="9" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="U13" s="9" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>1.5</v>
+        <v>0.71</v>
       </c>
       <c r="X13" s="9" t="n">
-        <v>0.75</v>
+        <v>0.58</v>
       </c>
       <c r="Y13" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="Z13" s="9" t="n">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="15">
@@ -19907,76 +19907,76 @@
         <v>0</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>6.25</v>
+        <v>5.31</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>6.25</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>6.25</v>
+        <v>6.04</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>6.25</v>
+        <v>5.73</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>6.5</v>
+        <v>5.49</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>6</v>
+        <v>4.78</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>6</v>
+        <v>4.57</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>6</v>
+        <v>5.17</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>7.75</v>
+        <v>6.81</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>7.5</v>
+        <v>6.28</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>8</v>
+        <v>6.35</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>8</v>
+        <v>7.12</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>8</v>
+        <v>6.61</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>7.5</v>
+        <v>5.69</v>
       </c>
       <c r="R17" s="9" t="n">
-        <v>6.75</v>
+        <v>4.89</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="T17" s="9" t="n">
-        <v>5</v>
+        <v>3.67</v>
       </c>
       <c r="U17" s="9" t="n">
-        <v>3.5</v>
+        <v>2.83</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="X17" s="9" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="Z17" s="9" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="18">
@@ -19989,76 +19989,76 @@
         <v>0</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0.75</v>
+        <v>0.52</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>5.75</v>
+        <v>4.85</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>5.75</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>5.75</v>
+        <v>5.54</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>5.75</v>
+        <v>5.16</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>5.75</v>
+        <v>4.77</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>5.25</v>
+        <v>4.28</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>5.25</v>
+        <v>4.02</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6</v>
+        <v>5.26</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>5.75</v>
+        <v>4.71</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>6.25</v>
+        <v>4.64</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>5.75</v>
+        <v>4.91</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>5.25</v>
+        <v>3.93</v>
       </c>
       <c r="R18" s="9" t="n">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="T18" s="9" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="U18" s="9" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>1.75</v>
+        <v>0.88</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="X18" s="9" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="Y18" s="9" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="Z18" s="9" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20">
@@ -20160,76 +20160,76 @@
         <v>0</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>6.75</v>
+        <v>6.08</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>6.52</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>8</v>
+        <v>6.07</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>7.75</v>
+        <v>6.3</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>7.25</v>
+        <v>5.33</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>8</v>
+        <v>6.29</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>7.5</v>
+        <v>5.51</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>7.25</v>
+        <v>5.47</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>7.5</v>
+        <v>6.38</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>7.5</v>
+        <v>6.35</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>7.75</v>
+        <v>5.73</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>6.5</v>
+        <v>5.47</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>7.75</v>
+        <v>6.2</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>6.75</v>
+        <v>5.99</v>
       </c>
       <c r="R22" s="9" t="n">
-        <v>6.75</v>
+        <v>5.97</v>
       </c>
       <c r="S22" s="9" t="n">
-        <v>6.25</v>
+        <v>5.11</v>
       </c>
       <c r="T22" s="9" t="n">
-        <v>5.75</v>
+        <v>4.55</v>
       </c>
       <c r="U22" s="9" t="n">
-        <v>4.25</v>
+        <v>3.46</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>3.75</v>
+        <v>1.94</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>2.25</v>
+        <v>1.52</v>
       </c>
       <c r="X22" s="9" t="n">
-        <v>2</v>
+        <v>1.09</v>
       </c>
       <c r="Y22" s="9" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="Z22" s="9" t="n">
-        <v>0.75</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="23">
@@ -20242,70 +20242,70 @@
         <v>0</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>0.75</v>
+        <v>1.21</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>6.5</v>
+        <v>5.83</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>6.75</v>
+        <v>6.27</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>6.75</v>
+        <v>5.56</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>6.25</v>
+        <v>4.83</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>7</v>
+        <v>5.58</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>6.75</v>
+        <v>5.02</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>6.25</v>
+        <v>5.01</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>6.75</v>
+        <v>5.63</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>6.75</v>
+        <v>5.66</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>7</v>
+        <v>4.84</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>5.5</v>
+        <v>4.34</v>
       </c>
       <c r="P23" s="9" t="n">
-        <v>6</v>
+        <v>4.87</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>5.25</v>
+        <v>4.86</v>
       </c>
       <c r="R23" s="9" t="n">
-        <v>5.25</v>
+        <v>4.68</v>
       </c>
       <c r="S23" s="9" t="n">
-        <v>4.75</v>
+        <v>3.76</v>
       </c>
       <c r="T23" s="9" t="n">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="U23" s="9" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="X23" s="9" t="n">
-        <v>0.75</v>
+        <v>0.09</v>
       </c>
       <c r="Y23" s="9" t="n">
         <v>0</v>
@@ -20413,76 +20413,76 @@
         <v>0</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>6</v>
+        <v>5.38</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>5.75</v>
+        <v>5.48</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>5.75</v>
+        <v>5.62</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>5.25</v>
+        <v>5.31</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>7</v>
+        <v>5.97</v>
       </c>
       <c r="M27" s="9" t="n">
-        <v>7</v>
+        <v>6.72</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>7.25</v>
+        <v>6.62</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>7.25</v>
+        <v>5.92</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>6.75</v>
+        <v>6.22</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="R27" s="9" t="n">
-        <v>6.5</v>
+        <v>5.81</v>
       </c>
       <c r="S27" s="9" t="n">
-        <v>6.75</v>
+        <v>5.84</v>
       </c>
       <c r="T27" s="9" t="n">
-        <v>6.25</v>
+        <v>4.38</v>
       </c>
       <c r="U27" s="9" t="n">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>2.75</v>
+        <v>1.68</v>
       </c>
       <c r="X27" s="9" t="n">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="Y27" s="9" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="Z27" s="9" t="n">
-        <v>0.75</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="28">
@@ -20495,76 +20495,76 @@
         <v>0</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>5.5</v>
+        <v>4.79</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>5.5</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>5.75</v>
+        <v>5.13</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>5.5</v>
+        <v>5.23</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>5.5</v>
+        <v>5.37</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>6.75</v>
+        <v>5.57</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>6.5</v>
+        <v>6.03</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>6.25</v>
+        <v>5.74</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>6.25</v>
+        <v>5.42</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>6.25</v>
+        <v>5.72</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>6.5</v>
+        <v>5.42</v>
       </c>
       <c r="R28" s="9" t="n">
-        <v>5.75</v>
+        <v>5.06</v>
       </c>
       <c r="S28" s="9" t="n">
-        <v>5.75</v>
+        <v>5.08</v>
       </c>
       <c r="T28" s="9" t="n">
-        <v>5.5</v>
+        <v>3.88</v>
       </c>
       <c r="U28" s="9" t="n">
-        <v>4</v>
+        <v>2.81</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>2</v>
+        <v>0.88</v>
       </c>
       <c r="X28" s="9" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="Y28" s="9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Z28" s="9" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="30">
@@ -21063,70 +21063,70 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>22</v>
+        <v>21.09990000000001</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="D4" s="20" t="n">
-        <v>2</v>
+        <v>1.1667</v>
       </c>
       <c r="E4" s="20" t="n">
-        <v>1</v>
+        <v>1.1667</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>0</v>
+        <v>0.5333</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H4" s="20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="20" t="n">
-        <v>3</v>
+        <v>1.7333</v>
       </c>
       <c r="J4" s="20" t="n">
-        <v>1</v>
+        <v>1.4333</v>
       </c>
       <c r="K4" s="20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L4" s="20" t="n">
-        <v>1</v>
+        <v>1.1667</v>
       </c>
       <c r="M4" s="20" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N4" s="20" t="n">
-        <v>1</v>
+        <v>1.2333</v>
       </c>
       <c r="O4" s="20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P4" s="20" t="n">
-        <v>1</v>
+        <v>1.3667</v>
       </c>
       <c r="Q4" s="20" t="n">
-        <v>1</v>
+        <v>0.9667</v>
       </c>
       <c r="R4" s="20" t="n">
-        <v>3</v>
+        <v>2.2333</v>
       </c>
       <c r="S4" s="20" t="n">
-        <v>1</v>
+        <v>0.5333</v>
       </c>
       <c r="T4" s="20" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U4" s="20" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="V4" s="20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="W4" s="20" t="n">
-        <v>1</v>
+        <v>1.3333</v>
       </c>
     </row>
     <row r="5">
@@ -21136,70 +21136,70 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>126</v>
+        <v>111.1667</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>6.3</v>
+        <v>5.56</v>
       </c>
       <c r="D5" s="20" t="n">
-        <v>7</v>
+        <v>6.1333</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>6</v>
+        <v>5.2333</v>
       </c>
       <c r="G5" s="20" t="n">
-        <v>6</v>
+        <v>5.2667</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="I5" s="20" t="n">
-        <v>6</v>
+        <v>5.5333</v>
       </c>
       <c r="J5" s="20" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="K5" s="20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L5" s="20" t="n">
-        <v>7</v>
+        <v>6.2667</v>
       </c>
       <c r="M5" s="20" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="N5" s="20" t="n">
-        <v>8</v>
+        <v>7.0667</v>
       </c>
       <c r="O5" s="20" t="n">
-        <v>6</v>
+        <v>4.4667</v>
       </c>
       <c r="P5" s="20" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="Q5" s="20" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="R5" s="20" t="n">
-        <v>6</v>
+        <v>5.4333</v>
       </c>
       <c r="S5" s="20" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="T5" s="20" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="U5" s="20" t="n">
-        <v>6</v>
+        <v>5.1667</v>
       </c>
       <c r="V5" s="20" t="n">
-        <v>6</v>
+        <v>5.8667</v>
       </c>
       <c r="W5" s="20" t="n">
-        <v>7</v>
+        <v>6.5333</v>
       </c>
     </row>
     <row r="6">
@@ -21209,16 +21209,16 @@
         </is>
       </c>
       <c r="B6" s="18" t="n">
-        <v>128</v>
+        <v>121.1001</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>6.4</v>
+        <v>6.06</v>
       </c>
       <c r="D6" s="20" t="n">
-        <v>7</v>
+        <v>6.2667</v>
       </c>
       <c r="E6" s="20" t="n">
-        <v>8</v>
+        <v>7.0333</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>6</v>
@@ -21230,28 +21230,28 @@
         <v>5</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>7</v>
+        <v>6.1333</v>
       </c>
       <c r="K6" s="20" t="n">
         <v>5</v>
       </c>
       <c r="L6" s="20" t="n">
-        <v>7</v>
+        <v>6.2667</v>
       </c>
       <c r="M6" s="20" t="n">
         <v>6</v>
       </c>
       <c r="N6" s="20" t="n">
-        <v>8</v>
+        <v>6.9667</v>
       </c>
       <c r="O6" s="20" t="n">
         <v>6</v>
       </c>
       <c r="P6" s="20" t="n">
-        <v>7</v>
+        <v>6.2667</v>
       </c>
       <c r="Q6" s="20" t="n">
         <v>5</v>
@@ -21263,16 +21263,16 @@
         <v>6</v>
       </c>
       <c r="T6" s="20" t="n">
-        <v>7</v>
+        <v>6.5667</v>
       </c>
       <c r="U6" s="20" t="n">
         <v>6</v>
       </c>
       <c r="V6" s="20" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="W6" s="20" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="7">
@@ -21282,70 +21282,70 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>130</v>
+        <v>111.7334</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>6.5</v>
+        <v>5.59</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>7</v>
+        <v>6.6667</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>6</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>6</v>
+        <v>4.7667</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>7</v>
+        <v>6.2667</v>
       </c>
       <c r="J7" s="20" t="n">
-        <v>7</v>
+        <v>5.4333</v>
       </c>
       <c r="K7" s="20" t="n">
         <v>5</v>
       </c>
       <c r="L7" s="20" t="n">
+        <v>4.9667</v>
+      </c>
+      <c r="M7" s="20" t="n">
+        <v>5.6333</v>
+      </c>
+      <c r="N7" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="M7" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N7" s="20" t="n">
-        <v>8</v>
-      </c>
       <c r="O7" s="20" t="n">
-        <v>6</v>
+        <v>5.9333</v>
       </c>
       <c r="P7" s="20" t="n">
-        <v>8</v>
+        <v>6.2667</v>
       </c>
       <c r="Q7" s="20" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="R7" s="20" t="n">
-        <v>6</v>
+        <v>5.3667</v>
       </c>
       <c r="S7" s="20" t="n">
-        <v>6</v>
+        <v>5.2333</v>
       </c>
       <c r="T7" s="20" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="U7" s="20" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="V7" s="20" t="n">
-        <v>6</v>
+        <v>4.4333</v>
       </c>
       <c r="W7" s="20" t="n">
-        <v>7</v>
+        <v>5.1667</v>
       </c>
     </row>
     <row r="8">
@@ -21355,70 +21355,70 @@
         </is>
       </c>
       <c r="B8" s="18" t="n">
-        <v>126</v>
+        <v>109.7669</v>
       </c>
       <c r="C8" s="19" t="n">
-        <v>6.3</v>
+        <v>5.49</v>
       </c>
       <c r="D8" s="20" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="E8" s="20" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>6</v>
+        <v>5.1667</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>6</v>
+        <v>4.5667</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>7</v>
+        <v>5.7333</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>7</v>
+        <v>5.5667</v>
       </c>
       <c r="K8" s="20" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L8" s="20" t="n">
-        <v>7</v>
+        <v>6.1667</v>
       </c>
       <c r="M8" s="20" t="n">
-        <v>6</v>
+        <v>5.2667</v>
       </c>
       <c r="N8" s="20" t="n">
-        <v>8</v>
+        <v>6.1667</v>
       </c>
       <c r="O8" s="20" t="n">
-        <v>6</v>
+        <v>5.1667</v>
       </c>
       <c r="P8" s="20" t="n">
-        <v>8</v>
+        <v>6.7333</v>
       </c>
       <c r="Q8" s="20" t="n">
-        <v>4</v>
+        <v>4.2667</v>
       </c>
       <c r="R8" s="20" t="n">
-        <v>5</v>
+        <v>4.5667</v>
       </c>
       <c r="S8" s="20" t="n">
         <v>6</v>
       </c>
       <c r="T8" s="20" t="n">
+        <v>4.7667</v>
+      </c>
+      <c r="U8" s="20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V8" s="20" t="n">
+        <v>5.1333</v>
+      </c>
+      <c r="W8" s="20" t="n">
         <v>6</v>
-      </c>
-      <c r="U8" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="W8" s="20" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -21428,70 +21428,70 @@
         </is>
       </c>
       <c r="B9" s="18" t="n">
-        <v>124</v>
+        <v>104.7999</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>6.2</v>
+        <v>5.24</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>6</v>
+        <v>6.1333</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>8</v>
+        <v>6.7333</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>6</v>
+        <v>5.4333</v>
       </c>
       <c r="G9" s="20" t="n">
-        <v>5</v>
+        <v>2.8667</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="J9" s="20" t="n">
-        <v>6</v>
+        <v>4.6333</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L9" s="20" t="n">
-        <v>7</v>
+        <v>5.5667</v>
       </c>
       <c r="M9" s="20" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="N9" s="20" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="O9" s="20" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="P9" s="20" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="Q9" s="20" t="n">
         <v>5</v>
       </c>
       <c r="R9" s="20" t="n">
-        <v>6</v>
+        <v>5.4333</v>
       </c>
       <c r="S9" s="20" t="n">
-        <v>6</v>
+        <v>4.4333</v>
       </c>
       <c r="T9" s="20" t="n">
+        <v>4.5667</v>
+      </c>
+      <c r="U9" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="U9" s="20" t="n">
-        <v>6</v>
-      </c>
       <c r="V9" s="20" t="n">
-        <v>6</v>
+        <v>5.0333</v>
       </c>
       <c r="W9" s="20" t="n">
-        <v>7</v>
+        <v>5.7667</v>
       </c>
     </row>
     <row r="10">
@@ -21501,70 +21501,70 @@
         </is>
       </c>
       <c r="B10" s="18" t="n">
-        <v>124</v>
+        <v>103.0999</v>
       </c>
       <c r="C10" s="19" t="n">
-        <v>6.2</v>
+        <v>5.15</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>6</v>
+        <v>4.7333</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>6</v>
+        <v>4.5333</v>
       </c>
       <c r="H10" s="20" t="n">
         <v>6</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>6</v>
+        <v>2.4333</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>5</v>
+        <v>4.3333</v>
       </c>
       <c r="L10" s="20" t="n">
-        <v>7</v>
+        <v>6.4333</v>
       </c>
       <c r="M10" s="20" t="n">
-        <v>6</v>
+        <v>5.4667</v>
       </c>
       <c r="N10" s="20" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="O10" s="20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P10" s="20" t="n">
-        <v>8</v>
+        <v>6.4333</v>
       </c>
       <c r="Q10" s="20" t="n">
         <v>5</v>
       </c>
       <c r="R10" s="20" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="S10" s="20" t="n">
-        <v>5</v>
+        <v>3.5667</v>
       </c>
       <c r="T10" s="20" t="n">
-        <v>7</v>
+        <v>4.9333</v>
       </c>
       <c r="U10" s="20" t="n">
         <v>5</v>
       </c>
       <c r="V10" s="20" t="n">
-        <v>6</v>
+        <v>5.3667</v>
       </c>
       <c r="W10" s="20" t="n">
-        <v>7</v>
+        <v>6.4667</v>
       </c>
     </row>
     <row r="11">
@@ -21574,70 +21574,70 @@
         </is>
       </c>
       <c r="B11" s="18" t="n">
-        <v>119</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>5.95</v>
+        <v>4.68</v>
       </c>
       <c r="D11" s="20" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="F11" s="20" t="n">
-        <v>6</v>
+        <v>3.8667</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="I11" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J11" s="20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K11" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="K11" s="20" t="n">
-        <v>5</v>
-      </c>
       <c r="L11" s="20" t="n">
-        <v>7</v>
+        <v>5.2667</v>
       </c>
       <c r="M11" s="20" t="n">
         <v>6</v>
       </c>
       <c r="N11" s="20" t="n">
-        <v>8</v>
+        <v>4.8333</v>
       </c>
       <c r="O11" s="20" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P11" s="20" t="n">
-        <v>7</v>
+        <v>3.6333</v>
       </c>
       <c r="Q11" s="20" t="n">
-        <v>5</v>
+        <v>4.1667</v>
       </c>
       <c r="R11" s="20" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="S11" s="20" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="T11" s="20" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="U11" s="20" t="n">
-        <v>5</v>
+        <v>4.5333</v>
       </c>
       <c r="V11" s="20" t="n">
-        <v>5</v>
+        <v>3.5333</v>
       </c>
       <c r="W11" s="20" t="n">
-        <v>7</v>
+        <v>5.6667</v>
       </c>
     </row>
     <row r="12">
@@ -21647,70 +21647,70 @@
         </is>
       </c>
       <c r="B12" s="18" t="n">
-        <v>113</v>
+        <v>94.2336</v>
       </c>
       <c r="C12" s="19" t="n">
-        <v>5.65</v>
+        <v>4.71</v>
       </c>
       <c r="D12" s="20" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>6</v>
+        <v>5.2667</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>5</v>
+        <v>3.6667</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>6</v>
+        <v>5.4333</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>5</v>
+        <v>4.8667</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>4</v>
+        <v>2.9667</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>4</v>
+        <v>3.8667</v>
       </c>
       <c r="L12" s="20" t="n">
-        <v>6</v>
+        <v>4.1667</v>
       </c>
       <c r="M12" s="20" t="n">
-        <v>6</v>
+        <v>6.1333</v>
       </c>
       <c r="N12" s="20" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="O12" s="20" t="n">
-        <v>5</v>
+        <v>4.4667</v>
       </c>
       <c r="P12" s="20" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="Q12" s="20" t="n">
-        <v>5</v>
+        <v>4.6667</v>
       </c>
       <c r="R12" s="20" t="n">
-        <v>6</v>
+        <v>4.7667</v>
       </c>
       <c r="S12" s="20" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="T12" s="20" t="n">
-        <v>7</v>
+        <v>6.1333</v>
       </c>
       <c r="U12" s="20" t="n">
-        <v>4</v>
+        <v>4.5667</v>
       </c>
       <c r="V12" s="20" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W12" s="20" t="n">
-        <v>7</v>
+        <v>4.0667</v>
       </c>
     </row>
     <row r="13">
@@ -21720,70 +21720,70 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>133</v>
+        <v>109.9666</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>6.65</v>
+        <v>5.5</v>
       </c>
       <c r="D13" s="20" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="G13" s="20" t="n">
-        <v>7</v>
+        <v>6.1333</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>6</v>
+        <v>4.7333</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>6</v>
+        <v>4.1333</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>6</v>
+        <v>4.8333</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>4</v>
+        <v>2.4667</v>
       </c>
       <c r="L13" s="20" t="n">
-        <v>7</v>
+        <v>5.4667</v>
       </c>
       <c r="M13" s="20" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="N13" s="20" t="n">
-        <v>9</v>
+        <v>7.3667</v>
       </c>
       <c r="O13" s="20" t="n">
-        <v>7</v>
+        <v>6.6333</v>
       </c>
       <c r="P13" s="20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q13" s="20" t="n">
-        <v>7</v>
+        <v>5.7333</v>
       </c>
       <c r="R13" s="20" t="n">
-        <v>6</v>
+        <v>5.0667</v>
       </c>
       <c r="S13" s="20" t="n">
-        <v>8</v>
+        <v>7.6333</v>
       </c>
       <c r="T13" s="20" t="n">
-        <v>8</v>
+        <v>6.4333</v>
       </c>
       <c r="U13" s="20" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="V13" s="20" t="n">
-        <v>6</v>
+        <v>5.7667</v>
       </c>
       <c r="W13" s="20" t="n">
-        <v>7</v>
+        <v>4.5667</v>
       </c>
     </row>
     <row r="14">
@@ -21793,70 +21793,70 @@
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>130</v>
+        <v>111.4332</v>
       </c>
       <c r="C14" s="19" t="n">
-        <v>6.5</v>
+        <v>5.57</v>
       </c>
       <c r="D14" s="20" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="E14" s="20" t="n">
-        <v>9</v>
+        <v>6.9333</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>5</v>
+        <v>3.7667</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>6</v>
+        <v>5.8333</v>
       </c>
       <c r="I14" s="20" t="n">
         <v>5</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="K14" s="20" t="n">
         <v>3</v>
       </c>
       <c r="L14" s="20" t="n">
-        <v>7</v>
+        <v>5.9333</v>
       </c>
       <c r="M14" s="20" t="n">
         <v>6</v>
       </c>
       <c r="N14" s="20" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="O14" s="20" t="n">
-        <v>7</v>
+        <v>5.1333</v>
       </c>
       <c r="P14" s="20" t="n">
-        <v>5</v>
+        <v>4.1667</v>
       </c>
       <c r="Q14" s="20" t="n">
-        <v>7</v>
+        <v>6.5333</v>
       </c>
       <c r="R14" s="20" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="S14" s="20" t="n">
-        <v>8</v>
+        <v>6.9333</v>
       </c>
       <c r="T14" s="20" t="n">
-        <v>8</v>
+        <v>6.3333</v>
       </c>
       <c r="U14" s="20" t="n">
-        <v>7</v>
+        <v>5.7333</v>
       </c>
       <c r="V14" s="20" t="n">
-        <v>6</v>
+        <v>5.2667</v>
       </c>
       <c r="W14" s="20" t="n">
-        <v>7</v>
+        <v>6.6667</v>
       </c>
     </row>
     <row r="15">
@@ -21866,70 +21866,70 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>131</v>
+        <v>107.9335</v>
       </c>
       <c r="C15" s="19" t="n">
-        <v>6.55</v>
+        <v>5.4</v>
       </c>
       <c r="D15" s="20" t="n">
-        <v>6</v>
+        <v>5.6667</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>5</v>
+        <v>4.5667</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>7</v>
+        <v>4.8333</v>
       </c>
       <c r="H15" s="20" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I15" s="20" t="n">
         <v>5</v>
       </c>
       <c r="J15" s="20" t="n">
-        <v>8</v>
+        <v>6.8667</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>7</v>
+        <v>5.3667</v>
       </c>
       <c r="M15" s="20" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="N15" s="20" t="n">
-        <v>9</v>
+        <v>7.6667</v>
       </c>
       <c r="O15" s="20" t="n">
-        <v>7</v>
+        <v>4.5667</v>
       </c>
       <c r="P15" s="20" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="Q15" s="20" t="n">
         <v>6</v>
       </c>
       <c r="R15" s="20" t="n">
-        <v>6</v>
+        <v>5.7333</v>
       </c>
       <c r="S15" s="20" t="n">
-        <v>8</v>
+        <v>5.4333</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>7</v>
+        <v>4.4667</v>
       </c>
       <c r="U15" s="20" t="n">
-        <v>7</v>
+        <v>5.5667</v>
       </c>
       <c r="V15" s="20" t="n">
-        <v>5</v>
+        <v>4.2667</v>
       </c>
       <c r="W15" s="20" t="n">
-        <v>7</v>
+        <v>6.0333</v>
       </c>
     </row>
     <row r="16">
@@ -21939,70 +21939,70 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>123</v>
+        <v>102.9665</v>
       </c>
       <c r="C16" s="19" t="n">
-        <v>6.15</v>
+        <v>5.15</v>
       </c>
       <c r="D16" s="20" t="n">
-        <v>6</v>
+        <v>5.2333</v>
       </c>
       <c r="E16" s="20" t="n">
-        <v>7</v>
+        <v>5.3333</v>
       </c>
       <c r="F16" s="20" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="G16" s="20" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="H16" s="20" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I16" s="20" t="n">
         <v>5</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L16" s="20" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="M16" s="20" t="n">
-        <v>6</v>
+        <v>4.3333</v>
       </c>
       <c r="N16" s="20" t="n">
-        <v>8</v>
+        <v>6.3333</v>
       </c>
       <c r="O16" s="20" t="n">
-        <v>7</v>
+        <v>6.1333</v>
       </c>
       <c r="P16" s="20" t="n">
-        <v>6</v>
+        <v>4.7667</v>
       </c>
       <c r="Q16" s="20" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="R16" s="20" t="n">
-        <v>6</v>
+        <v>4.3333</v>
       </c>
       <c r="S16" s="20" t="n">
-        <v>7</v>
+        <v>6.1667</v>
       </c>
       <c r="T16" s="20" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="U16" s="20" t="n">
-        <v>7</v>
+        <v>6.2333</v>
       </c>
       <c r="V16" s="20" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="W16" s="20" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="17">
@@ -22012,70 +22012,70 @@
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>119</v>
+        <v>102.4001</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>5.95</v>
+        <v>5.12</v>
       </c>
       <c r="D17" s="20" t="n">
-        <v>6</v>
+        <v>5.5667</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>6</v>
+        <v>5.3333</v>
       </c>
       <c r="F17" s="20" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="G17" s="20" t="n">
-        <v>6</v>
+        <v>4.7667</v>
       </c>
       <c r="H17" s="20" t="n">
-        <v>7</v>
+        <v>5.8667</v>
       </c>
       <c r="I17" s="20" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="J17" s="20" t="n">
-        <v>7</v>
+        <v>5.3667</v>
       </c>
       <c r="K17" s="20" t="n">
-        <v>4</v>
+        <v>3.7667</v>
       </c>
       <c r="L17" s="20" t="n">
-        <v>6</v>
+        <v>4.4667</v>
       </c>
       <c r="M17" s="20" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="N17" s="20" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="O17" s="20" t="n">
-        <v>7</v>
+        <v>6.1333</v>
       </c>
       <c r="P17" s="20" t="n">
-        <v>6</v>
+        <v>4.9333</v>
       </c>
       <c r="Q17" s="20" t="n">
-        <v>6</v>
+        <v>5.6333</v>
       </c>
       <c r="R17" s="20" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="S17" s="20" t="n">
-        <v>7</v>
+        <v>5.8333</v>
       </c>
       <c r="T17" s="20" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="U17" s="20" t="n">
-        <v>6</v>
+        <v>6.1667</v>
       </c>
       <c r="V17" s="20" t="n">
-        <v>5</v>
+        <v>4.5667</v>
       </c>
       <c r="W17" s="20" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="18">
@@ -22085,70 +22085,70 @@
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>115</v>
+        <v>94.63330000000001</v>
       </c>
       <c r="C18" s="19" t="n">
-        <v>5.75</v>
+        <v>4.73</v>
       </c>
       <c r="D18" s="20" t="n">
-        <v>6</v>
+        <v>5.3667</v>
       </c>
       <c r="E18" s="20" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="F18" s="20" t="n">
-        <v>4</v>
+        <v>3.0667</v>
       </c>
       <c r="G18" s="20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H18" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="H18" s="20" t="n">
-        <v>6</v>
-      </c>
       <c r="I18" s="20" t="n">
-        <v>5</v>
+        <v>3.8333</v>
       </c>
       <c r="J18" s="20" t="n">
-        <v>6</v>
+        <v>5.3667</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>4</v>
+        <v>3.1667</v>
       </c>
       <c r="L18" s="20" t="n">
         <v>5</v>
       </c>
       <c r="M18" s="20" t="n">
-        <v>6</v>
+        <v>4.1333</v>
       </c>
       <c r="N18" s="20" t="n">
-        <v>7</v>
+        <v>5.4333</v>
       </c>
       <c r="O18" s="20" t="n">
-        <v>6</v>
+        <v>4.8333</v>
       </c>
       <c r="P18" s="20" t="n">
-        <v>5</v>
+        <v>4.4333</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>7</v>
+        <v>6.2333</v>
       </c>
       <c r="R18" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S18" s="20" t="n">
-        <v>7</v>
+        <v>4.6667</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="U18" s="20" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="V18" s="20" t="n">
-        <v>5</v>
+        <v>2.7667</v>
       </c>
       <c r="W18" s="20" t="n">
-        <v>8</v>
+        <v>7.3333</v>
       </c>
     </row>
     <row r="19">
@@ -22158,10 +22158,10 @@
         </is>
       </c>
       <c r="B19" s="18" t="n">
-        <v>101</v>
+        <v>86.6001</v>
       </c>
       <c r="C19" s="19" t="n">
-        <v>5.05</v>
+        <v>4.33</v>
       </c>
       <c r="D19" s="20" t="n">
         <v>6</v>
@@ -22170,22 +22170,22 @@
         <v>4</v>
       </c>
       <c r="F19" s="20" t="n">
-        <v>4</v>
+        <v>2.0333</v>
       </c>
       <c r="G19" s="20" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H19" s="20" t="n">
-        <v>6</v>
+        <v>4.9333</v>
       </c>
       <c r="I19" s="20" t="n">
-        <v>5</v>
+        <v>3.8667</v>
       </c>
       <c r="J19" s="20" t="n">
-        <v>5</v>
+        <v>3.7667</v>
       </c>
       <c r="K19" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L19" s="20" t="n">
         <v>5</v>
@@ -22194,34 +22194,34 @@
         <v>5</v>
       </c>
       <c r="N19" s="20" t="n">
-        <v>7</v>
+        <v>6.3333</v>
       </c>
       <c r="O19" s="20" t="n">
+        <v>4.7667</v>
+      </c>
+      <c r="P19" s="20" t="n">
+        <v>3.4667</v>
+      </c>
+      <c r="Q19" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="P19" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="20" t="n">
-        <v>6</v>
-      </c>
       <c r="R19" s="20" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="S19" s="20" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="T19" s="20" t="n">
-        <v>5</v>
+        <v>4.5667</v>
       </c>
       <c r="U19" s="20" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="V19" s="20" t="n">
-        <v>2</v>
+        <v>1.5667</v>
       </c>
       <c r="W19" s="20" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="20">
@@ -22231,70 +22231,70 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>91</v>
+        <v>73.30000000000001</v>
       </c>
       <c r="C20" s="19" t="n">
-        <v>4.55</v>
+        <v>3.67</v>
       </c>
       <c r="D20" s="20" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="E20" s="20" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="F20" s="20" t="n">
         <v>2</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>6</v>
+        <v>4.0333</v>
       </c>
       <c r="H20" s="20" t="n">
-        <v>7</v>
+        <v>5.9667</v>
       </c>
       <c r="I20" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J20" s="20" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="K20" s="20" t="n">
         <v>2</v>
       </c>
       <c r="L20" s="20" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="M20" s="20" t="n">
-        <v>5</v>
+        <v>4.7333</v>
       </c>
       <c r="N20" s="20" t="n">
-        <v>6</v>
+        <v>4.8333</v>
       </c>
       <c r="O20" s="20" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="P20" s="20" t="n">
+        <v>3.6333</v>
+      </c>
+      <c r="Q20" s="20" t="n">
+        <v>4.0667</v>
+      </c>
+      <c r="R20" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="Q20" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="R20" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="S20" s="20" t="n">
-        <v>5</v>
-      </c>
       <c r="T20" s="20" t="n">
-        <v>4</v>
+        <v>3.9667</v>
       </c>
       <c r="U20" s="20" t="n">
-        <v>6</v>
+        <v>5.5667</v>
       </c>
       <c r="V20" s="20" t="n">
         <v>2</v>
       </c>
       <c r="W20" s="20" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="21">
@@ -22304,19 +22304,19 @@
         </is>
       </c>
       <c r="B21" s="18" t="n">
-        <v>75</v>
+        <v>56.0334</v>
       </c>
       <c r="C21" s="19" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="D21" s="20" t="n">
-        <v>3</v>
+        <v>2.5667</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>3</v>
+        <v>2.0333</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G21" s="20" t="n">
         <v>4</v>
@@ -22331,43 +22331,43 @@
         <v>1</v>
       </c>
       <c r="K21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M21" s="20" t="n">
+        <v>3.9667</v>
+      </c>
+      <c r="N21" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L21" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="N21" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" s="20" t="n">
+      <c r="P21" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="P21" s="20" t="n">
-        <v>4</v>
-      </c>
       <c r="Q21" s="20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R21" s="20" t="n">
-        <v>2</v>
+        <v>1.7667</v>
       </c>
       <c r="S21" s="20" t="n">
         <v>4</v>
       </c>
       <c r="T21" s="20" t="n">
-        <v>4</v>
+        <v>2.9667</v>
       </c>
       <c r="U21" s="20" t="n">
-        <v>6</v>
+        <v>3.5333</v>
       </c>
       <c r="V21" s="20" t="n">
         <v>2</v>
       </c>
       <c r="W21" s="20" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="22">
@@ -22377,67 +22377,67 @@
         </is>
       </c>
       <c r="B22" s="18" t="n">
-        <v>54</v>
+        <v>40.5333</v>
       </c>
       <c r="C22" s="19" t="n">
-        <v>2.7</v>
+        <v>2.03</v>
       </c>
       <c r="D22" s="20" t="n">
-        <v>3</v>
+        <v>1.3333</v>
       </c>
       <c r="E22" s="20" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="F22" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>4</v>
+        <v>2.3667</v>
       </c>
       <c r="H22" s="20" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="I22" s="20" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J22" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="20" t="n">
-        <v>1</v>
+        <v>0.2667</v>
       </c>
       <c r="L22" s="20" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="M22" s="20" t="n">
-        <v>4</v>
+        <v>2.2333</v>
       </c>
       <c r="N22" s="20" t="n">
         <v>4</v>
       </c>
       <c r="O22" s="20" t="n">
-        <v>2</v>
+        <v>1.7333</v>
       </c>
       <c r="P22" s="20" t="n">
-        <v>3</v>
+        <v>2.4667</v>
       </c>
       <c r="Q22" s="20" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="R22" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S22" s="20" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T22" s="20" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="U22" s="20" t="n">
         <v>3</v>
       </c>
       <c r="V22" s="20" t="n">
-        <v>2</v>
+        <v>0.3333</v>
       </c>
       <c r="W22" s="20" t="n">
         <v>3</v>
@@ -22450,10 +22450,10 @@
         </is>
       </c>
       <c r="B23" s="18" t="n">
-        <v>39</v>
+        <v>25.6334</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>1.95</v>
+        <v>1.28</v>
       </c>
       <c r="D23" s="20" t="n">
         <v>1</v>
@@ -22462,37 +22462,37 @@
         <v>1</v>
       </c>
       <c r="F23" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G23" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="H23" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="20" t="n">
-        <v>3</v>
-      </c>
       <c r="I23" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" s="20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="20" t="n">
+        <v>1.8667</v>
+      </c>
+      <c r="M23" s="20" t="n">
+        <v>0.5667</v>
+      </c>
+      <c r="N23" s="20" t="n">
+        <v>2.9667</v>
+      </c>
+      <c r="O23" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="O23" s="20" t="n">
-        <v>2</v>
-      </c>
       <c r="P23" s="20" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="Q23" s="20" t="n">
         <v>2</v>
@@ -22501,10 +22501,10 @@
         <v>1</v>
       </c>
       <c r="S23" s="20" t="n">
-        <v>4</v>
+        <v>2.0333</v>
       </c>
       <c r="T23" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" s="20" t="n">
         <v>3</v>
@@ -22513,7 +22513,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="20" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="24">
@@ -22523,16 +22523,16 @@
         </is>
       </c>
       <c r="B24" s="18" t="n">
-        <v>26</v>
+        <v>16.3001</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>1.3</v>
+        <v>0.82</v>
       </c>
       <c r="D24" s="20" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="20" t="n">
-        <v>1</v>
+        <v>0.0667</v>
       </c>
       <c r="F24" s="20" t="n">
         <v>1</v>
@@ -22541,34 +22541,34 @@
         <v>1</v>
       </c>
       <c r="H24" s="20" t="n">
-        <v>2</v>
+        <v>0.2667</v>
       </c>
       <c r="I24" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J24" s="20" t="n">
-        <v>2</v>
+        <v>0.6667</v>
       </c>
       <c r="K24" s="20" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="20" t="n">
-        <v>2</v>
+        <v>0.6333</v>
       </c>
       <c r="M24" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="20" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="O24" s="20" t="n">
-        <v>1</v>
+        <v>0.7333</v>
       </c>
       <c r="P24" s="20" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="20" t="n">
-        <v>2</v>
+        <v>1.2667</v>
       </c>
       <c r="R24" s="20" t="n">
         <v>1</v>
@@ -22577,10 +22577,10 @@
         <v>2</v>
       </c>
       <c r="T24" s="20" t="n">
-        <v>1</v>
+        <v>0.5667</v>
       </c>
       <c r="U24" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V24" s="20" t="n">
         <v>0</v>
@@ -22596,10 +22596,10 @@
         </is>
       </c>
       <c r="B25" s="18" t="n">
-        <v>17</v>
+        <v>10.3667</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>0.85</v>
+        <v>0.52</v>
       </c>
       <c r="D25" s="20" t="n">
         <v>1</v>
@@ -22608,25 +22608,25 @@
         <v>0</v>
       </c>
       <c r="F25" s="20" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="G25" s="20" t="n">
-        <v>1</v>
+        <v>0.3667</v>
       </c>
       <c r="H25" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="20" t="n">
-        <v>2</v>
+        <v>1.4667</v>
       </c>
       <c r="J25" s="20" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="K25" s="20" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="20" t="n">
         <v>0</v>
@@ -22635,22 +22635,22 @@
         <v>1</v>
       </c>
       <c r="O25" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="20" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="20" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="R25" s="20" t="n">
         <v>1</v>
       </c>
       <c r="S25" s="20" t="n">
-        <v>2</v>
+        <v>1.1333</v>
       </c>
       <c r="T25" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" s="20" t="n">
         <v>2</v>
@@ -22669,10 +22669,10 @@
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>9</v>
+        <v>6.899999999999999</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
       <c r="D26" s="20" t="n">
         <v>1</v>
@@ -22681,7 +22681,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="20" t="n">
         <v>0</v>
@@ -22690,7 +22690,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="20" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J26" s="20" t="n">
         <v>0</v>
@@ -22726,7 +22726,7 @@
         <v>0</v>
       </c>
       <c r="U26" s="20" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="V26" s="20" t="n">
         <v>0</v>
@@ -22742,13 +22742,13 @@
         </is>
       </c>
       <c r="B27" s="18" t="n">
-        <v>7</v>
+        <v>0.1998</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="D27" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="E27" s="20" t="n">
         <v>0</v>
@@ -22763,7 +22763,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="20" t="n">
         <v>0</v>
@@ -22778,7 +22778,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="O27" s="20" t="n">
         <v>0</v>
@@ -22790,22 +22790,22 @@
         <v>0</v>
       </c>
       <c r="R27" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="S27" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="T27" s="20" t="n">
         <v>0</v>
       </c>
       <c r="U27" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="V27" s="20" t="n">
         <v>0</v>
       </c>
       <c r="W27" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
     </row>
     <row r="29">
@@ -23012,10 +23012,10 @@
         </is>
       </c>
       <c r="B32" s="18" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="C32" s="19" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="D32" s="20" t="n">
         <v>0</v>
@@ -23027,7 +23027,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="H32" s="20" t="n">
         <v>0</v>
@@ -23039,7 +23039,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="20" t="n">
-        <v>0</v>
+        <v>0.1333</v>
       </c>
       <c r="L32" s="20" t="n">
         <v>0</v>
@@ -23072,7 +23072,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W32" s="20" t="n">
         <v>0</v>
@@ -23085,10 +23085,10 @@
         </is>
       </c>
       <c r="B33" s="18" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.45</v>
+        <v>0.37</v>
       </c>
       <c r="D33" s="20" t="n">
         <v>0</v>
@@ -23106,10 +23106,10 @@
         <v>0</v>
       </c>
       <c r="I33" s="20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J33" s="20" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K33" s="20" t="n">
         <v>1</v>
@@ -23118,7 +23118,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="20" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N33" s="20" t="n">
         <v>0</v>
@@ -23133,10 +23133,10 @@
         <v>0</v>
       </c>
       <c r="R33" s="20" t="n">
-        <v>2</v>
+        <v>1.3667</v>
       </c>
       <c r="S33" s="20" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="T33" s="20" t="n">
         <v>0</v>
@@ -23231,10 +23231,10 @@
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>12</v>
+        <v>10.8667</v>
       </c>
       <c r="C35" s="19" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="D35" s="20" t="n">
         <v>0</v>
@@ -23246,7 +23246,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>2</v>
+        <v>1.7333</v>
       </c>
       <c r="H35" s="20" t="n">
         <v>0</v>
@@ -23261,7 +23261,7 @@
         <v>1</v>
       </c>
       <c r="L35" s="20" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="M35" s="20" t="n">
         <v>1</v>
@@ -23285,13 +23285,13 @@
         <v>1</v>
       </c>
       <c r="T35" s="20" t="n">
-        <v>1</v>
+        <v>0.2667</v>
       </c>
       <c r="U35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="V35" s="20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="W35" s="20" t="n">
         <v>0</v>
@@ -23304,13 +23304,13 @@
         </is>
       </c>
       <c r="B36" s="18" t="n">
-        <v>15</v>
+        <v>13.4</v>
       </c>
       <c r="C36" s="19" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="D36" s="20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E36" s="20" t="n">
         <v>0</v>
@@ -23319,7 +23319,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>2</v>
+        <v>1.4667</v>
       </c>
       <c r="H36" s="20" t="n">
         <v>0</v>
@@ -23328,7 +23328,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="20" t="n">
-        <v>2</v>
+        <v>1.6333</v>
       </c>
       <c r="K36" s="20" t="n">
         <v>1</v>
@@ -23358,7 +23358,7 @@
         <v>1</v>
       </c>
       <c r="T36" s="20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U36" s="20" t="n">
         <v>0</v>
@@ -23377,10 +23377,10 @@
         </is>
       </c>
       <c r="B37" s="18" t="n">
-        <v>15</v>
+        <v>12.6334</v>
       </c>
       <c r="C37" s="19" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="D37" s="20" t="n">
         <v>1</v>
@@ -23392,7 +23392,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="20" t="n">
-        <v>2</v>
+        <v>1.5667</v>
       </c>
       <c r="H37" s="20" t="n">
         <v>0</v>
@@ -23407,7 +23407,7 @@
         <v>1</v>
       </c>
       <c r="L37" s="20" t="n">
-        <v>1</v>
+        <v>0.2667</v>
       </c>
       <c r="M37" s="20" t="n">
         <v>1</v>
@@ -23425,13 +23425,13 @@
         <v>0</v>
       </c>
       <c r="R37" s="20" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="S37" s="20" t="n">
         <v>1</v>
       </c>
       <c r="T37" s="20" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="U37" s="20" t="n">
         <v>0</v>
@@ -23450,10 +23450,10 @@
         </is>
       </c>
       <c r="B38" s="18" t="n">
-        <v>15</v>
+        <v>12.8333</v>
       </c>
       <c r="C38" s="19" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="D38" s="20" t="n">
         <v>1</v>
@@ -23465,7 +23465,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>2</v>
+        <v>1.2667</v>
       </c>
       <c r="H38" s="20" t="n">
         <v>0</v>
@@ -23480,7 +23480,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="20" t="n">
-        <v>1</v>
+        <v>0.7333</v>
       </c>
       <c r="M38" s="20" t="n">
         <v>1</v>
@@ -23498,13 +23498,13 @@
         <v>0</v>
       </c>
       <c r="R38" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S38" s="20" t="n">
         <v>1</v>
       </c>
       <c r="T38" s="20" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="U38" s="20" t="n">
         <v>0</v>
@@ -23523,10 +23523,10 @@
         </is>
       </c>
       <c r="B39" s="18" t="n">
-        <v>14</v>
+        <v>11.3001</v>
       </c>
       <c r="C39" s="19" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="D39" s="20" t="n">
         <v>1</v>
@@ -23547,13 +23547,13 @@
         <v>1</v>
       </c>
       <c r="J39" s="20" t="n">
-        <v>2</v>
+        <v>1.1667</v>
       </c>
       <c r="K39" s="20" t="n">
         <v>1</v>
       </c>
       <c r="L39" s="20" t="n">
-        <v>1</v>
+        <v>0.2667</v>
       </c>
       <c r="M39" s="20" t="n">
         <v>1</v>
@@ -23562,7 +23562,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="20" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="P39" s="20" t="n">
         <v>0</v>
@@ -23574,10 +23574,10 @@
         <v>1</v>
       </c>
       <c r="S39" s="20" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="T39" s="20" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="U39" s="20" t="n">
         <v>0</v>
@@ -23596,10 +23596,10 @@
         </is>
       </c>
       <c r="B40" s="18" t="n">
-        <v>17</v>
+        <v>11.9333</v>
       </c>
       <c r="C40" s="19" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="D40" s="20" t="n">
         <v>1</v>
@@ -23608,7 +23608,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>1</v>
@@ -23617,16 +23617,16 @@
         <v>0</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K40" s="20" t="n">
-        <v>3</v>
+        <v>2.3333</v>
       </c>
       <c r="L40" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="20" t="n">
         <v>1</v>
@@ -23638,7 +23638,7 @@
         <v>1</v>
       </c>
       <c r="P40" s="20" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="Q40" s="20" t="n">
         <v>0</v>
@@ -23647,19 +23647,19 @@
         <v>1</v>
       </c>
       <c r="S40" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U40" s="20" t="n">
         <v>0</v>
       </c>
       <c r="V40" s="20" t="n">
-        <v>2</v>
+        <v>1.1667</v>
       </c>
       <c r="W40" s="20" t="n">
-        <v>1</v>
+        <v>0.6333</v>
       </c>
     </row>
     <row r="41">
@@ -23669,10 +23669,10 @@
         </is>
       </c>
       <c r="B41" s="18" t="n">
-        <v>18</v>
+        <v>19.3333</v>
       </c>
       <c r="C41" s="19" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="D41" s="20" t="n">
         <v>1</v>
@@ -23681,7 +23681,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="20" t="n">
-        <v>2</v>
+        <v>1.5333</v>
       </c>
       <c r="G41" s="20" t="n">
         <v>1</v>
@@ -23690,22 +23690,22 @@
         <v>0</v>
       </c>
       <c r="I41" s="20" t="n">
+        <v>1.0333</v>
+      </c>
+      <c r="J41" s="20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K41" s="20" t="n">
+        <v>3.6667</v>
+      </c>
+      <c r="L41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N41" s="20" t="n">
         <v>1</v>
-      </c>
-      <c r="J41" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" s="20" t="n">
-        <v>0</v>
       </c>
       <c r="O41" s="20" t="n">
         <v>1</v>
@@ -23714,7 +23714,7 @@
         <v>2</v>
       </c>
       <c r="Q41" s="20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R41" s="20" t="n">
         <v>1</v>
@@ -23723,7 +23723,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U41" s="20" t="n">
         <v>0</v>
@@ -23742,10 +23742,10 @@
         </is>
       </c>
       <c r="B42" s="18" t="n">
-        <v>20</v>
+        <v>21.2334</v>
       </c>
       <c r="C42" s="19" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="D42" s="20" t="n">
         <v>1</v>
@@ -23754,7 +23754,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2</v>
+        <v>2.3333</v>
       </c>
       <c r="G42" s="20" t="n">
         <v>1</v>
@@ -23763,31 +23763,31 @@
         <v>0</v>
       </c>
       <c r="I42" s="20" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J42" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="20" t="n">
-        <v>4</v>
+        <v>2.9667</v>
       </c>
       <c r="L42" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M42" s="20" t="n">
+        <v>1.4667</v>
+      </c>
+      <c r="N42" s="20" t="n">
         <v>1</v>
-      </c>
-      <c r="N42" s="20" t="n">
-        <v>0</v>
       </c>
       <c r="O42" s="20" t="n">
         <v>1</v>
       </c>
       <c r="P42" s="20" t="n">
-        <v>2</v>
+        <v>1.7667</v>
       </c>
       <c r="Q42" s="20" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="R42" s="20" t="n">
         <v>1</v>
@@ -23796,13 +23796,13 @@
         <v>0</v>
       </c>
       <c r="T42" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42" s="20" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="W42" s="20" t="n">
         <v>1</v>
@@ -23815,16 +23815,16 @@
         </is>
       </c>
       <c r="B43" s="18" t="n">
-        <v>24</v>
+        <v>22.5668</v>
       </c>
       <c r="C43" s="19" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="D43" s="20" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>1</v>
+        <v>0.8667</v>
       </c>
       <c r="F43" s="20" t="n">
         <v>3</v>
@@ -23836,40 +23836,40 @@
         <v>0</v>
       </c>
       <c r="I43" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="20" t="n">
-        <v>4</v>
+        <v>2.5667</v>
       </c>
       <c r="L43" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M43" s="20" t="n">
-        <v>2</v>
+        <v>1.7667</v>
       </c>
       <c r="N43" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" s="20" t="n">
         <v>1</v>
       </c>
       <c r="P43" s="20" t="n">
-        <v>2</v>
+        <v>1.3333</v>
       </c>
       <c r="Q43" s="20" t="n">
-        <v>2</v>
+        <v>1.7667</v>
       </c>
       <c r="R43" s="20" t="n">
         <v>1</v>
       </c>
       <c r="S43" s="20" t="n">
-        <v>0</v>
+        <v>0.2667</v>
       </c>
       <c r="T43" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" s="20" t="n">
         <v>0</v>
@@ -23888,19 +23888,19 @@
         </is>
       </c>
       <c r="B44" s="18" t="n">
-        <v>23</v>
+        <v>22.6334</v>
       </c>
       <c r="C44" s="19" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="D44" s="20" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="E44" s="20" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G44" s="20" t="n">
         <v>1</v>
@@ -23915,16 +23915,16 @@
         <v>1</v>
       </c>
       <c r="K44" s="20" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="L44" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M44" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N44" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="20" t="n">
         <v>1</v>
@@ -23933,7 +23933,7 @@
         <v>2</v>
       </c>
       <c r="Q44" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R44" s="20" t="n">
         <v>1</v>
@@ -23942,7 +23942,7 @@
         <v>1</v>
       </c>
       <c r="T44" s="20" t="n">
-        <v>0</v>
+        <v>0.8667</v>
       </c>
       <c r="U44" s="20" t="n">
         <v>0</v>
@@ -23961,46 +23961,46 @@
         </is>
       </c>
       <c r="B45" s="18" t="n">
-        <v>26</v>
+        <v>21.1334</v>
       </c>
       <c r="C45" s="19" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="D45" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="20" t="n">
         <v>2</v>
       </c>
       <c r="F45" s="20" t="n">
-        <v>3</v>
+        <v>1.6667</v>
       </c>
       <c r="G45" s="20" t="n">
-        <v>2</v>
+        <v>1.3333</v>
       </c>
       <c r="H45" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="20" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="J45" s="20" t="n">
-        <v>1</v>
+        <v>0.5667</v>
       </c>
       <c r="K45" s="20" t="n">
         <v>4</v>
       </c>
       <c r="L45" s="20" t="n">
-        <v>1</v>
+        <v>0.8667</v>
       </c>
       <c r="M45" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N45" s="20" t="n">
-        <v>0</v>
+        <v>0.9667</v>
       </c>
       <c r="O45" s="20" t="n">
-        <v>1</v>
+        <v>0.1333</v>
       </c>
       <c r="P45" s="20" t="n">
         <v>2</v>
@@ -24021,10 +24021,10 @@
         <v>0</v>
       </c>
       <c r="V45" s="20" t="n">
-        <v>2</v>
+        <v>1.8667</v>
       </c>
       <c r="W45" s="20" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="46">
@@ -24034,10 +24034,10 @@
         </is>
       </c>
       <c r="B46" s="18" t="n">
-        <v>23</v>
+        <v>18.9666</v>
       </c>
       <c r="C46" s="19" t="n">
-        <v>1.15</v>
+        <v>0.95</v>
       </c>
       <c r="D46" s="20" t="n">
         <v>0</v>
@@ -24046,10 +24046,10 @@
         <v>2</v>
       </c>
       <c r="F46" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>2</v>
+        <v>0.5333</v>
       </c>
       <c r="H46" s="20" t="n">
         <v>0</v>
@@ -24058,19 +24058,19 @@
         <v>0</v>
       </c>
       <c r="J46" s="20" t="n">
-        <v>1</v>
+        <v>0.4667</v>
       </c>
       <c r="K46" s="20" t="n">
-        <v>4</v>
+        <v>3.6333</v>
       </c>
       <c r="L46" s="20" t="n">
         <v>1</v>
       </c>
       <c r="M46" s="20" t="n">
-        <v>1</v>
+        <v>1.1333</v>
       </c>
       <c r="N46" s="20" t="n">
-        <v>1</v>
+        <v>1.3667</v>
       </c>
       <c r="O46" s="20" t="n">
         <v>0</v>
@@ -24082,7 +24082,7 @@
         <v>1</v>
       </c>
       <c r="R46" s="20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="S46" s="20" t="n">
         <v>1</v>
@@ -24094,7 +24094,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="20" t="n">
-        <v>3</v>
+        <v>1.6333</v>
       </c>
       <c r="W46" s="20" t="n">
         <v>0</v>
@@ -24107,19 +24107,19 @@
         </is>
       </c>
       <c r="B47" s="18" t="n">
-        <v>25</v>
+        <v>22.7667</v>
       </c>
       <c r="C47" s="19" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="D47" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="F47" s="20" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G47" s="20" t="n">
         <v>0</v>
@@ -24131,13 +24131,13 @@
         <v>0</v>
       </c>
       <c r="J47" s="20" t="n">
-        <v>2</v>
+        <v>1.8667</v>
       </c>
       <c r="K47" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L47" s="20" t="n">
-        <v>2</v>
+        <v>1.5667</v>
       </c>
       <c r="M47" s="20" t="n">
         <v>2</v>
@@ -24155,10 +24155,10 @@
         <v>1</v>
       </c>
       <c r="R47" s="20" t="n">
-        <v>2</v>
+        <v>1.7333</v>
       </c>
       <c r="S47" s="20" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T47" s="20" t="n">
         <v>1</v>
@@ -24180,25 +24180,25 @@
         </is>
       </c>
       <c r="B48" s="18" t="n">
-        <v>28</v>
+        <v>22.66670000000001</v>
       </c>
       <c r="C48" s="19" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="D48" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="20" t="n">
-        <v>2</v>
+        <v>0.4333</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>3</v>
+        <v>2.8333</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H48" s="20" t="n">
-        <v>1</v>
+        <v>0.9667</v>
       </c>
       <c r="I48" s="20" t="n">
         <v>0</v>
@@ -24207,16 +24207,16 @@
         <v>2</v>
       </c>
       <c r="K48" s="20" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="L48" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M48" s="20" t="n">
         <v>2</v>
       </c>
       <c r="N48" s="20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O48" s="20" t="n">
         <v>0</v>
@@ -24225,10 +24225,10 @@
         <v>2</v>
       </c>
       <c r="Q48" s="20" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="R48" s="20" t="n">
         <v>1</v>
-      </c>
-      <c r="R48" s="20" t="n">
-        <v>2</v>
       </c>
       <c r="S48" s="20" t="n">
         <v>2</v>
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="20" t="n">
-        <v>3</v>
+        <v>2.8667</v>
       </c>
       <c r="W48" s="20" t="n">
         <v>0</v>
@@ -24253,19 +24253,19 @@
         </is>
       </c>
       <c r="B49" s="18" t="n">
-        <v>25</v>
+        <v>19.6</v>
       </c>
       <c r="C49" s="19" t="n">
-        <v>1.25</v>
+        <v>0.98</v>
       </c>
       <c r="D49" s="20" t="n">
-        <v>1</v>
+        <v>0.9667</v>
       </c>
       <c r="E49" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="20" t="n">
         <v>1</v>
@@ -24280,16 +24280,16 @@
         <v>2</v>
       </c>
       <c r="K49" s="20" t="n">
-        <v>2</v>
+        <v>1.2667</v>
       </c>
       <c r="L49" s="20" t="n">
-        <v>2</v>
+        <v>0.7333</v>
       </c>
       <c r="M49" s="20" t="n">
-        <v>2</v>
+        <v>1.0333</v>
       </c>
       <c r="N49" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O49" s="20" t="n">
         <v>0</v>
@@ -24301,7 +24301,7 @@
         <v>0</v>
       </c>
       <c r="R49" s="20" t="n">
-        <v>1</v>
+        <v>0.7667</v>
       </c>
       <c r="S49" s="20" t="n">
         <v>2</v>
@@ -24313,7 +24313,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="20" t="n">
-        <v>3</v>
+        <v>2.8333</v>
       </c>
       <c r="W49" s="20" t="n">
         <v>0</v>
@@ -24326,10 +24326,10 @@
         </is>
       </c>
       <c r="B50" s="18" t="n">
-        <v>20</v>
+        <v>15.7333</v>
       </c>
       <c r="C50" s="19" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="D50" s="20" t="n">
         <v>1</v>
@@ -24338,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>2</v>
+        <v>0.7333</v>
       </c>
       <c r="G50" s="20" t="n">
         <v>1</v>
@@ -24359,10 +24359,10 @@
         <v>1</v>
       </c>
       <c r="M50" s="20" t="n">
-        <v>1</v>
+        <v>0.2333</v>
       </c>
       <c r="N50" s="20" t="n">
-        <v>1</v>
+        <v>0.3667</v>
       </c>
       <c r="O50" s="20" t="n">
         <v>0</v>
@@ -24374,19 +24374,19 @@
         <v>0</v>
       </c>
       <c r="R50" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="20" t="n">
         <v>2</v>
       </c>
       <c r="T50" s="20" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="U50" s="20" t="n">
         <v>0</v>
       </c>
       <c r="V50" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W50" s="20" t="n">
         <v>0</v>
@@ -24399,19 +24399,19 @@
         </is>
       </c>
       <c r="B51" s="18" t="n">
-        <v>16</v>
+        <v>10.6667</v>
       </c>
       <c r="C51" s="19" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="D51" s="20" t="n">
-        <v>1</v>
+        <v>0.1333</v>
       </c>
       <c r="E51" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="20" t="n">
         <v>1</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="20" t="n">
-        <v>2</v>
+        <v>1.3667</v>
       </c>
       <c r="K51" s="20" t="n">
         <v>1</v>
@@ -24441,7 +24441,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="20" t="n">
-        <v>2</v>
+        <v>0.0667</v>
       </c>
       <c r="Q51" s="20" t="n">
         <v>0</v>
@@ -24453,13 +24453,13 @@
         <v>2</v>
       </c>
       <c r="T51" s="20" t="n">
-        <v>2</v>
+        <v>1.4333</v>
       </c>
       <c r="U51" s="20" t="n">
         <v>0</v>
       </c>
       <c r="V51" s="20" t="n">
-        <v>2</v>
+        <v>1.6667</v>
       </c>
       <c r="W51" s="20" t="n">
         <v>0</v>
@@ -24472,10 +24472,10 @@
         </is>
       </c>
       <c r="B52" s="18" t="n">
-        <v>12</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C52" s="19" t="n">
-        <v>0.6</v>
+        <v>0.43</v>
       </c>
       <c r="D52" s="20" t="n">
         <v>0</v>
@@ -24499,7 +24499,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="20" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="L52" s="20" t="n">
         <v>1</v>
@@ -24514,7 +24514,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="20" t="n">
-        <v>2</v>
+        <v>0.8667</v>
       </c>
       <c r="Q52" s="20" t="n">
         <v>0</v>
@@ -24532,7 +24532,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="20" t="n">
-        <v>2</v>
+        <v>0.5333</v>
       </c>
       <c r="W52" s="20" t="n">
         <v>0</v>
@@ -24545,10 +24545,10 @@
         </is>
       </c>
       <c r="B53" s="18" t="n">
-        <v>9</v>
+        <v>7.166700000000001</v>
       </c>
       <c r="C53" s="19" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="D53" s="20" t="n">
         <v>0</v>
@@ -24569,7 +24569,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="20" t="n">
-        <v>1</v>
+        <v>0.1667</v>
       </c>
       <c r="K53" s="20" t="n">
         <v>0</v>
@@ -24587,7 +24587,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="20" t="n">
         <v>0</v>
@@ -24618,10 +24618,10 @@
         </is>
       </c>
       <c r="B54" s="18" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="C54" s="19" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="D54" s="20" t="n">
         <v>0</v>
@@ -24633,7 +24633,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="20" t="n">
-        <v>1</v>
+        <v>0.3667</v>
       </c>
       <c r="H54" s="20" t="n">
         <v>1</v>
@@ -24648,7 +24648,7 @@
         <v>0</v>
       </c>
       <c r="L54" s="20" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M54" s="20" t="n">
         <v>0</v>
@@ -24672,7 +24672,7 @@
         <v>2</v>
       </c>
       <c r="T54" s="20" t="n">
-        <v>1</v>
+        <v>0.6333</v>
       </c>
       <c r="U54" s="20" t="n">
         <v>0</v>
@@ -24691,10 +24691,10 @@
         </is>
       </c>
       <c r="B55" s="18" t="n">
-        <v>6</v>
+        <v>0.1333</v>
       </c>
       <c r="C55" s="19" t="n">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="D55" s="20" t="n">
         <v>0</v>
@@ -24709,7 +24709,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="I55" s="20" t="n">
         <v>0</v>
@@ -24721,7 +24721,7 @@
         <v>0</v>
       </c>
       <c r="L55" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="20" t="n">
         <v>0</v>
@@ -24733,7 +24733,7 @@
         <v>0</v>
       </c>
       <c r="P55" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="Q55" s="20" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="S55" s="20" t="n">
-        <v>2</v>
+        <v>0.0667</v>
       </c>
       <c r="T55" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U55" s="20" t="n">
         <v>0</v>
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="B61" s="18" t="n">
-        <v>1</v>
+        <v>0.9333</v>
       </c>
       <c r="C61" s="19" t="n">
         <v>0.05</v>
@@ -25052,7 +25052,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="20" t="n">
-        <v>1</v>
+        <v>0.9333</v>
       </c>
       <c r="I61" s="20" t="n">
         <v>0</v>
@@ -25107,10 +25107,10 @@
         </is>
       </c>
       <c r="B62" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" s="19" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D62" s="20" t="n">
         <v>0</v>
@@ -25125,7 +25125,7 @@
         <v>0</v>
       </c>
       <c r="H62" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" s="20" t="n">
         <v>0</v>
@@ -25253,10 +25253,10 @@
         </is>
       </c>
       <c r="B64" s="18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C64" s="19" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D64" s="20" t="n">
         <v>0</v>
@@ -25280,7 +25280,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="20" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L64" s="20" t="n">
         <v>0</v>
@@ -25326,10 +25326,10 @@
         </is>
       </c>
       <c r="B65" s="18" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C65" s="19" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D65" s="20" t="n">
         <v>0</v>
@@ -25353,7 +25353,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="20" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L65" s="20" t="n">
         <v>0</v>
@@ -25399,10 +25399,10 @@
         </is>
       </c>
       <c r="B66" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" s="19" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D66" s="20" t="n">
         <v>0</v>
@@ -25426,7 +25426,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="20" t="n">
         <v>0</v>
@@ -25472,10 +25472,10 @@
         </is>
       </c>
       <c r="B67" s="18" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C67" s="19" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D67" s="20" t="n">
         <v>0</v>
@@ -25496,7 +25496,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K67" s="20" t="n">
         <v>0</v>
@@ -25618,10 +25618,10 @@
         </is>
       </c>
       <c r="B69" s="18" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="C69" s="19" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="D69" s="20" t="n">
         <v>0</v>
@@ -25642,7 +25642,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="20" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K69" s="20" t="n">
         <v>0</v>
@@ -25691,10 +25691,10 @@
         </is>
       </c>
       <c r="B70" s="18" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="C70" s="19" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D70" s="20" t="n">
         <v>0</v>
@@ -25712,7 +25712,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="J70" s="20" t="n">
         <v>0</v>
@@ -25764,13 +25764,13 @@
         </is>
       </c>
       <c r="B71" s="18" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="C71" s="19" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="D71" s="20" t="n">
-        <v>1</v>
+        <v>0.5667</v>
       </c>
       <c r="E71" s="20" t="n">
         <v>0</v>
@@ -25794,7 +25794,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="20" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="M71" s="20" t="n">
         <v>0</v>
@@ -25837,10 +25837,10 @@
         </is>
       </c>
       <c r="B72" s="18" t="n">
-        <v>3</v>
+        <v>2.3667</v>
       </c>
       <c r="C72" s="19" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="D72" s="20" t="n">
         <v>1</v>
@@ -25858,7 +25858,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>1</v>
+        <v>0.3667</v>
       </c>
       <c r="J72" s="20" t="n">
         <v>0</v>
@@ -25910,10 +25910,10 @@
         </is>
       </c>
       <c r="B73" s="18" t="n">
-        <v>2</v>
+        <v>1.4333</v>
       </c>
       <c r="C73" s="19" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D73" s="20" t="n">
         <v>1</v>
@@ -25931,7 +25931,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="20" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J73" s="20" t="n">
         <v>0</v>
@@ -25940,7 +25940,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="20" t="n">
-        <v>1</v>
+        <v>0.1333</v>
       </c>
       <c r="M73" s="20" t="n">
         <v>0</v>
@@ -25983,19 +25983,19 @@
         </is>
       </c>
       <c r="B74" s="18" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="C74" s="19" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D74" s="20" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E74" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="20" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="G74" s="20" t="n">
         <v>0</v>
@@ -26022,7 +26022,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="20" t="n">
-        <v>1</v>
+        <v>0.5667</v>
       </c>
       <c r="P74" s="20" t="n">
         <v>0</v>
@@ -26056,19 +26056,19 @@
         </is>
       </c>
       <c r="B75" s="18" t="n">
-        <v>6</v>
+        <v>2.5333</v>
       </c>
       <c r="C75" s="19" t="n">
-        <v>0.3</v>
+        <v>0.13</v>
       </c>
       <c r="D75" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="20" t="n">
-        <v>1</v>
+        <v>0.4333</v>
       </c>
       <c r="G75" s="20" t="n">
         <v>0</v>
@@ -26083,10 +26083,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="20" t="n">
-        <v>1</v>
+        <v>0.5333</v>
       </c>
       <c r="L75" s="20" t="n">
-        <v>1</v>
+        <v>0.5667</v>
       </c>
       <c r="M75" s="20" t="n">
         <v>0</v>
@@ -26095,7 +26095,7 @@
         <v>0</v>
       </c>
       <c r="O75" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P75" s="20" t="n">
         <v>0</v>
@@ -26129,10 +26129,10 @@
         </is>
       </c>
       <c r="B76" s="18" t="n">
-        <v>4</v>
+        <v>2.6667</v>
       </c>
       <c r="C76" s="19" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="D76" s="20" t="n">
         <v>0</v>
@@ -26156,7 +26156,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="20" t="n">
         <v>1</v>
@@ -26168,7 +26168,7 @@
         <v>0</v>
       </c>
       <c r="O76" s="20" t="n">
-        <v>1</v>
+        <v>0.2667</v>
       </c>
       <c r="P76" s="20" t="n">
         <v>0</v>
@@ -26180,7 +26180,7 @@
         <v>0</v>
       </c>
       <c r="S76" s="20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="T76" s="20" t="n">
         <v>0</v>
@@ -26202,10 +26202,10 @@
         </is>
       </c>
       <c r="B77" s="18" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="C77" s="19" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="D77" s="20" t="n">
         <v>0</v>
@@ -26241,7 +26241,7 @@
         <v>0</v>
       </c>
       <c r="O77" s="20" t="n">
-        <v>1</v>
+        <v>0.9667</v>
       </c>
       <c r="P77" s="20" t="n">
         <v>0</v>
@@ -26250,10 +26250,10 @@
         <v>0</v>
       </c>
       <c r="R77" s="20" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="S77" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="T77" s="20" t="n">
         <v>0</v>
@@ -26275,13 +26275,13 @@
         </is>
       </c>
       <c r="B78" s="18" t="n">
-        <v>7</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="C78" s="19" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="D78" s="20" t="n">
-        <v>1</v>
+        <v>0.7667</v>
       </c>
       <c r="E78" s="20" t="n">
         <v>0</v>
@@ -26305,10 +26305,10 @@
         <v>0</v>
       </c>
       <c r="L78" s="20" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M78" s="20" t="n">
-        <v>1</v>
+        <v>0.9333</v>
       </c>
       <c r="N78" s="20" t="n">
         <v>0</v>
@@ -26335,7 +26335,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="20" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W78" s="20" t="n">
         <v>0</v>
@@ -26348,10 +26348,10 @@
         </is>
       </c>
       <c r="B79" s="18" t="n">
-        <v>7</v>
+        <v>4.699999999999999</v>
       </c>
       <c r="C79" s="19" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="D79" s="20" t="n">
         <v>1</v>
@@ -26369,7 +26369,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="20" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J79" s="20" t="n">
         <v>0</v>
@@ -26378,7 +26378,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="20" t="n">
         <v>1</v>
@@ -26387,7 +26387,7 @@
         <v>0</v>
       </c>
       <c r="O79" s="20" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="P79" s="20" t="n">
         <v>0</v>
@@ -26421,10 +26421,10 @@
         </is>
       </c>
       <c r="B80" s="18" t="n">
-        <v>6</v>
+        <v>6.233300000000001</v>
       </c>
       <c r="C80" s="19" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="D80" s="20" t="n">
         <v>1</v>
@@ -26439,7 +26439,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="20" t="n">
-        <v>0</v>
+        <v>0.4667</v>
       </c>
       <c r="I80" s="20" t="n">
         <v>0</v>
@@ -26448,13 +26448,13 @@
         <v>0</v>
       </c>
       <c r="K80" s="20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L80" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M80" s="20" t="n">
-        <v>2</v>
+        <v>1.7333</v>
       </c>
       <c r="N80" s="20" t="n">
         <v>0</v>
@@ -26481,10 +26481,10 @@
         <v>0</v>
       </c>
       <c r="V80" s="20" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W80" s="20" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="81">
@@ -26494,13 +26494,13 @@
         </is>
       </c>
       <c r="B81" s="18" t="n">
-        <v>8</v>
+        <v>5.1334</v>
       </c>
       <c r="C81" s="19" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="D81" s="20" t="n">
-        <v>1</v>
+        <v>0.8667</v>
       </c>
       <c r="E81" s="20" t="n">
         <v>0</v>
@@ -26527,7 +26527,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="20" t="n">
-        <v>2</v>
+        <v>0.2667</v>
       </c>
       <c r="N81" s="20" t="n">
         <v>0</v>
@@ -26554,7 +26554,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W81" s="20" t="n">
         <v>1</v>
@@ -26567,13 +26567,13 @@
         </is>
       </c>
       <c r="B82" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C82" s="19" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D82" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" s="20" t="n">
         <v>0</v>
@@ -26615,13 +26615,13 @@
         <v>0</v>
       </c>
       <c r="R82" s="20" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="S82" s="20" t="n">
         <v>0</v>
       </c>
       <c r="T82" s="20" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="U82" s="20" t="n">
         <v>0</v>
@@ -26640,10 +26640,10 @@
         </is>
       </c>
       <c r="B83" s="18" t="n">
-        <v>3</v>
+        <v>0.1332</v>
       </c>
       <c r="C83" s="19" t="n">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="D83" s="20" t="n">
         <v>0</v>
@@ -26658,7 +26658,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="I83" s="20" t="n">
         <v>0</v>
@@ -26667,7 +26667,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="L83" s="20" t="n">
         <v>0</v>
@@ -26694,7 +26694,7 @@
         <v>0</v>
       </c>
       <c r="T83" s="20" t="n">
-        <v>0</v>
+        <v>0.0333</v>
       </c>
       <c r="U83" s="20" t="n">
         <v>0</v>
@@ -26703,7 +26703,7 @@
         <v>0</v>
       </c>
       <c r="W83" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
     </row>
     <row r="85">
@@ -26910,70 +26910,70 @@
         </is>
       </c>
       <c r="B88" s="18" t="n">
-        <v>25</v>
+        <v>23.3999</v>
       </c>
       <c r="C88" s="19" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="D88" s="20" t="n">
-        <v>2</v>
+        <v>1.1667</v>
       </c>
       <c r="E88" s="20" t="n">
-        <v>1</v>
+        <v>1.1667</v>
       </c>
       <c r="F88" s="20" t="n">
-        <v>0</v>
+        <v>0.5333</v>
       </c>
       <c r="G88" s="20" t="n">
-        <v>1</v>
+        <v>1.4667</v>
       </c>
       <c r="H88" s="20" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I88" s="20" t="n">
-        <v>3</v>
+        <v>1.7333</v>
       </c>
       <c r="J88" s="20" t="n">
-        <v>1</v>
+        <v>1.4333</v>
       </c>
       <c r="K88" s="20" t="n">
-        <v>1</v>
+        <v>0.6333</v>
       </c>
       <c r="L88" s="20" t="n">
-        <v>1</v>
+        <v>1.1667</v>
       </c>
       <c r="M88" s="20" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N88" s="20" t="n">
-        <v>1</v>
+        <v>1.2333</v>
       </c>
       <c r="O88" s="20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P88" s="20" t="n">
-        <v>1</v>
+        <v>1.3667</v>
       </c>
       <c r="Q88" s="20" t="n">
-        <v>1</v>
+        <v>0.9667</v>
       </c>
       <c r="R88" s="20" t="n">
-        <v>3</v>
+        <v>2.2333</v>
       </c>
       <c r="S88" s="20" t="n">
-        <v>1</v>
+        <v>0.5333</v>
       </c>
       <c r="T88" s="20" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U88" s="20" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="V88" s="20" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="W88" s="20" t="n">
-        <v>1</v>
+        <v>1.3333</v>
       </c>
     </row>
     <row r="89">
@@ -26983,70 +26983,70 @@
         </is>
       </c>
       <c r="B89" s="18" t="n">
-        <v>136</v>
+        <v>119.5</v>
       </c>
       <c r="C89" s="19" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="D89" s="20" t="n">
+        <v>6.1333</v>
+      </c>
+      <c r="E89" s="20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F89" s="20" t="n">
+        <v>5.2333</v>
+      </c>
+      <c r="G89" s="20" t="n">
+        <v>6.2667</v>
+      </c>
+      <c r="H89" s="20" t="n">
+        <v>5.5333</v>
+      </c>
+      <c r="I89" s="20" t="n">
+        <v>6.3333</v>
+      </c>
+      <c r="J89" s="20" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K89" s="20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L89" s="20" t="n">
+        <v>6.2667</v>
+      </c>
+      <c r="M89" s="20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="N89" s="20" t="n">
+        <v>7.0667</v>
+      </c>
+      <c r="O89" s="20" t="n">
+        <v>4.4667</v>
+      </c>
+      <c r="P89" s="20" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q89" s="20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R89" s="20" t="n">
         <v>6.8</v>
       </c>
-      <c r="D89" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="E89" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F89" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G89" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="H89" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I89" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="J89" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="K89" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L89" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="M89" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="N89" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="O89" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="P89" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q89" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="R89" s="20" t="n">
-        <v>8</v>
-      </c>
       <c r="S89" s="20" t="n">
-        <v>7</v>
+        <v>6.0333</v>
       </c>
       <c r="T89" s="20" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="U89" s="20" t="n">
-        <v>6</v>
+        <v>5.1667</v>
       </c>
       <c r="V89" s="20" t="n">
-        <v>7</v>
+        <v>6.8667</v>
       </c>
       <c r="W89" s="20" t="n">
-        <v>7</v>
+        <v>6.5333</v>
       </c>
     </row>
     <row r="90">
@@ -27056,16 +27056,16 @@
         </is>
       </c>
       <c r="B90" s="18" t="n">
-        <v>138</v>
+        <v>130.1001</v>
       </c>
       <c r="C90" s="19" t="n">
-        <v>6.9</v>
+        <v>6.51</v>
       </c>
       <c r="D90" s="20" t="n">
-        <v>7</v>
+        <v>6.2667</v>
       </c>
       <c r="E90" s="20" t="n">
-        <v>8</v>
+        <v>7.0333</v>
       </c>
       <c r="F90" s="20" t="n">
         <v>6</v>
@@ -27074,31 +27074,31 @@
         <v>7</v>
       </c>
       <c r="H90" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I90" s="20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J90" s="20" t="n">
-        <v>8</v>
+        <v>7.1333</v>
       </c>
       <c r="K90" s="20" t="n">
         <v>6</v>
       </c>
       <c r="L90" s="20" t="n">
-        <v>7</v>
+        <v>6.2667</v>
       </c>
       <c r="M90" s="20" t="n">
         <v>7</v>
       </c>
       <c r="N90" s="20" t="n">
-        <v>8</v>
+        <v>6.9667</v>
       </c>
       <c r="O90" s="20" t="n">
         <v>6</v>
       </c>
       <c r="P90" s="20" t="n">
-        <v>7</v>
+        <v>6.2667</v>
       </c>
       <c r="Q90" s="20" t="n">
         <v>5</v>
@@ -27110,16 +27110,16 @@
         <v>7</v>
       </c>
       <c r="T90" s="20" t="n">
-        <v>7</v>
+        <v>6.5667</v>
       </c>
       <c r="U90" s="20" t="n">
         <v>6</v>
       </c>
       <c r="V90" s="20" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="W90" s="20" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="91">
@@ -27129,70 +27129,70 @@
         </is>
       </c>
       <c r="B91" s="18" t="n">
-        <v>142</v>
+        <v>122.6</v>
       </c>
       <c r="C91" s="19" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="D91" s="20" t="n">
+        <v>6.6667</v>
+      </c>
+      <c r="E91" s="20" t="n">
         <v>7.1</v>
-      </c>
-      <c r="D91" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="E91" s="20" t="n">
-        <v>8</v>
       </c>
       <c r="F91" s="20" t="n">
         <v>6</v>
       </c>
       <c r="G91" s="20" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="H91" s="20" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I91" s="20" t="n">
-        <v>8</v>
+        <v>7.2667</v>
       </c>
       <c r="J91" s="20" t="n">
-        <v>8</v>
+        <v>6.4333</v>
       </c>
       <c r="K91" s="20" t="n">
         <v>6</v>
       </c>
       <c r="L91" s="20" t="n">
-        <v>8</v>
+        <v>5.6333</v>
       </c>
       <c r="M91" s="20" t="n">
+        <v>6.6333</v>
+      </c>
+      <c r="N91" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="N91" s="20" t="n">
-        <v>8</v>
-      </c>
       <c r="O91" s="20" t="n">
-        <v>6</v>
+        <v>5.9333</v>
       </c>
       <c r="P91" s="20" t="n">
-        <v>8</v>
+        <v>6.2667</v>
       </c>
       <c r="Q91" s="20" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="R91" s="20" t="n">
-        <v>8</v>
+        <v>7.3667</v>
       </c>
       <c r="S91" s="20" t="n">
-        <v>7</v>
+        <v>6.2333</v>
       </c>
       <c r="T91" s="20" t="n">
-        <v>8</v>
+        <v>5.8667</v>
       </c>
       <c r="U91" s="20" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="V91" s="20" t="n">
-        <v>7</v>
+        <v>5.6333</v>
       </c>
       <c r="W91" s="20" t="n">
-        <v>7</v>
+        <v>5.1667</v>
       </c>
     </row>
     <row r="92">
@@ -27202,70 +27202,70 @@
         </is>
       </c>
       <c r="B92" s="18" t="n">
-        <v>140</v>
+        <v>123.4668</v>
       </c>
       <c r="C92" s="19" t="n">
-        <v>7</v>
+        <v>6.17</v>
       </c>
       <c r="D92" s="20" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="E92" s="20" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F92" s="20" t="n">
-        <v>6</v>
+        <v>5.1667</v>
       </c>
       <c r="G92" s="20" t="n">
-        <v>8</v>
+        <v>6.0333</v>
       </c>
       <c r="H92" s="20" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>8</v>
+        <v>6.7333</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="K92" s="20" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="L92" s="20" t="n">
-        <v>8</v>
+        <v>7.1667</v>
       </c>
       <c r="M92" s="20" t="n">
-        <v>7</v>
+        <v>6.2667</v>
       </c>
       <c r="N92" s="20" t="n">
-        <v>8</v>
+        <v>6.1667</v>
       </c>
       <c r="O92" s="20" t="n">
-        <v>6</v>
+        <v>5.1667</v>
       </c>
       <c r="P92" s="20" t="n">
-        <v>8</v>
+        <v>6.7333</v>
       </c>
       <c r="Q92" s="20" t="n">
-        <v>4</v>
+        <v>4.2667</v>
       </c>
       <c r="R92" s="20" t="n">
-        <v>7</v>
+        <v>6.5667</v>
       </c>
       <c r="S92" s="20" t="n">
         <v>7</v>
       </c>
       <c r="T92" s="20" t="n">
-        <v>7</v>
+        <v>5.2667</v>
       </c>
       <c r="U92" s="20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V92" s="20" t="n">
+        <v>7.1333</v>
+      </c>
+      <c r="W92" s="20" t="n">
         <v>6</v>
-      </c>
-      <c r="V92" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="W92" s="20" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -27275,70 +27275,70 @@
         </is>
       </c>
       <c r="B93" s="18" t="n">
-        <v>140</v>
+        <v>118.3331</v>
       </c>
       <c r="C93" s="19" t="n">
-        <v>7</v>
+        <v>5.92</v>
       </c>
       <c r="D93" s="20" t="n">
-        <v>7</v>
+        <v>7.1333</v>
       </c>
       <c r="E93" s="20" t="n">
-        <v>8</v>
+        <v>6.7333</v>
       </c>
       <c r="F93" s="20" t="n">
-        <v>6</v>
+        <v>5.4333</v>
       </c>
       <c r="G93" s="20" t="n">
-        <v>7</v>
+        <v>4.4333</v>
       </c>
       <c r="H93" s="20" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I93" s="20" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="J93" s="20" t="n">
-        <v>8</v>
+        <v>6.6333</v>
       </c>
       <c r="K93" s="20" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="L93" s="20" t="n">
-        <v>8</v>
+        <v>5.8333</v>
       </c>
       <c r="M93" s="20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="N93" s="20" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="O93" s="20" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="P93" s="20" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="Q93" s="20" t="n">
         <v>5</v>
       </c>
       <c r="R93" s="20" t="n">
-        <v>8</v>
+        <v>7.0333</v>
       </c>
       <c r="S93" s="20" t="n">
-        <v>7</v>
+        <v>5.4333</v>
       </c>
       <c r="T93" s="20" t="n">
-        <v>6</v>
+        <v>4.7667</v>
       </c>
       <c r="U93" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V93" s="20" t="n">
-        <v>8</v>
+        <v>7.0333</v>
       </c>
       <c r="W93" s="20" t="n">
-        <v>7</v>
+        <v>5.7667</v>
       </c>
     </row>
     <row r="94">
@@ -27348,70 +27348,70 @@
         </is>
       </c>
       <c r="B94" s="18" t="n">
-        <v>140</v>
+        <v>115.9334</v>
       </c>
       <c r="C94" s="19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D94" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="D94" s="20" t="n">
-        <v>8</v>
-      </c>
       <c r="E94" s="20" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="F94" s="20" t="n">
-        <v>6</v>
+        <v>4.7333</v>
       </c>
       <c r="G94" s="20" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="H94" s="20" t="n">
         <v>6</v>
       </c>
       <c r="I94" s="20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>8</v>
+        <v>4.4333</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>7</v>
+        <v>5.3333</v>
       </c>
       <c r="L94" s="20" t="n">
-        <v>8</v>
+        <v>7.1667</v>
       </c>
       <c r="M94" s="20" t="n">
-        <v>7</v>
+        <v>6.4667</v>
       </c>
       <c r="N94" s="20" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="O94" s="20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P94" s="20" t="n">
-        <v>8</v>
+        <v>6.4333</v>
       </c>
       <c r="Q94" s="20" t="n">
         <v>5</v>
       </c>
       <c r="R94" s="20" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="S94" s="20" t="n">
-        <v>6</v>
+        <v>4.5667</v>
       </c>
       <c r="T94" s="20" t="n">
-        <v>8</v>
+        <v>5.7667</v>
       </c>
       <c r="U94" s="20" t="n">
         <v>5</v>
       </c>
       <c r="V94" s="20" t="n">
-        <v>8</v>
+        <v>7.3667</v>
       </c>
       <c r="W94" s="20" t="n">
-        <v>7</v>
+        <v>6.4667</v>
       </c>
     </row>
     <row r="95">
@@ -27421,70 +27421,70 @@
         </is>
       </c>
       <c r="B95" s="18" t="n">
-        <v>134</v>
+        <v>105.7</v>
       </c>
       <c r="C95" s="19" t="n">
-        <v>6.7</v>
+        <v>5.29</v>
       </c>
       <c r="D95" s="20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="E95" s="20" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="F95" s="20" t="n">
+        <v>3.8667</v>
+      </c>
+      <c r="G95" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="G95" s="20" t="n">
-        <v>7</v>
-      </c>
       <c r="H95" s="20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I95" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="I95" s="20" t="n">
-        <v>7</v>
-      </c>
       <c r="J95" s="20" t="n">
-        <v>7</v>
+        <v>5.4667</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L95" s="20" t="n">
-        <v>8</v>
+        <v>5.5333</v>
       </c>
       <c r="M95" s="20" t="n">
         <v>7</v>
       </c>
       <c r="N95" s="20" t="n">
-        <v>8</v>
+        <v>4.8333</v>
       </c>
       <c r="O95" s="20" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="P95" s="20" t="n">
-        <v>7</v>
+        <v>3.6333</v>
       </c>
       <c r="Q95" s="20" t="n">
-        <v>5</v>
+        <v>4.1667</v>
       </c>
       <c r="R95" s="20" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="S95" s="20" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="T95" s="20" t="n">
-        <v>8</v>
+        <v>6.8667</v>
       </c>
       <c r="U95" s="20" t="n">
-        <v>5</v>
+        <v>4.5333</v>
       </c>
       <c r="V95" s="20" t="n">
-        <v>7</v>
+        <v>5.5333</v>
       </c>
       <c r="W95" s="20" t="n">
-        <v>7</v>
+        <v>5.6667</v>
       </c>
     </row>
     <row r="96">
@@ -27494,70 +27494,70 @@
         </is>
       </c>
       <c r="B96" s="18" t="n">
-        <v>129</v>
+        <v>107.1668</v>
       </c>
       <c r="C96" s="19" t="n">
-        <v>6.45</v>
+        <v>5.36</v>
       </c>
       <c r="D96" s="20" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>6</v>
+        <v>5.2667</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>5</v>
+        <v>3.8333</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>7</v>
+        <v>6.4333</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>5</v>
+        <v>4.8667</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>6</v>
+        <v>5.2667</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>7</v>
+        <v>4.1667</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>7</v>
+        <v>7.1333</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>6</v>
+        <v>5.4667</v>
       </c>
       <c r="P96" s="20" t="n">
-        <v>7</v>
+        <v>5.1333</v>
       </c>
       <c r="Q96" s="20" t="n">
-        <v>5</v>
+        <v>4.6667</v>
       </c>
       <c r="R96" s="20" t="n">
-        <v>7</v>
+        <v>5.7667</v>
       </c>
       <c r="S96" s="20" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="T96" s="20" t="n">
-        <v>8</v>
+        <v>6.1333</v>
       </c>
       <c r="U96" s="20" t="n">
-        <v>4</v>
+        <v>4.5667</v>
       </c>
       <c r="V96" s="20" t="n">
-        <v>8</v>
+        <v>5.7667</v>
       </c>
       <c r="W96" s="20" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="97">
@@ -27567,70 +27567,70 @@
         </is>
       </c>
       <c r="B97" s="18" t="n">
-        <v>152</v>
+        <v>127.5999</v>
       </c>
       <c r="C97" s="19" t="n">
-        <v>7.6</v>
+        <v>6.38</v>
       </c>
       <c r="D97" s="20" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="F97" s="20" t="n">
-        <v>7</v>
+        <v>5.8333</v>
       </c>
       <c r="G97" s="20" t="n">
-        <v>8</v>
+        <v>7.1333</v>
       </c>
       <c r="H97" s="20" t="n">
-        <v>6</v>
+        <v>4.7333</v>
       </c>
       <c r="I97" s="20" t="n">
-        <v>7</v>
+        <v>5.1667</v>
       </c>
       <c r="J97" s="20" t="n">
-        <v>9</v>
+        <v>6.6333</v>
       </c>
       <c r="K97" s="20" t="n">
-        <v>8</v>
+        <v>6.1333</v>
       </c>
       <c r="L97" s="20" t="n">
-        <v>7</v>
+        <v>5.4667</v>
       </c>
       <c r="M97" s="20" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="N97" s="20" t="n">
-        <v>9</v>
+        <v>7.3667</v>
       </c>
       <c r="O97" s="20" t="n">
-        <v>8</v>
+        <v>7.6333</v>
       </c>
       <c r="P97" s="20" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q97" s="20" t="n">
-        <v>7</v>
+        <v>6.1333</v>
       </c>
       <c r="R97" s="20" t="n">
-        <v>7</v>
+        <v>6.0667</v>
       </c>
       <c r="S97" s="20" t="n">
-        <v>8</v>
+        <v>7.6333</v>
       </c>
       <c r="T97" s="20" t="n">
-        <v>8</v>
+        <v>6.4333</v>
       </c>
       <c r="U97" s="20" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="V97" s="20" t="n">
-        <v>7</v>
+        <v>6.7667</v>
       </c>
       <c r="W97" s="20" t="n">
-        <v>8</v>
+        <v>5.5667</v>
       </c>
     </row>
     <row r="98">
@@ -27640,70 +27640,70 @@
         </is>
       </c>
       <c r="B98" s="18" t="n">
-        <v>151</v>
+        <v>132.0331</v>
       </c>
       <c r="C98" s="19" t="n">
-        <v>7.55</v>
+        <v>6.6</v>
       </c>
       <c r="D98" s="20" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="E98" s="20" t="n">
-        <v>9</v>
+        <v>6.9333</v>
       </c>
       <c r="F98" s="20" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="G98" s="20" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="H98" s="20" t="n">
-        <v>6</v>
+        <v>5.8333</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>8</v>
+        <v>7.4333</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>7</v>
+        <v>5.9667</v>
       </c>
       <c r="L98" s="20" t="n">
-        <v>7</v>
+        <v>5.9333</v>
       </c>
       <c r="M98" s="20" t="n">
-        <v>7</v>
+        <v>7.4667</v>
       </c>
       <c r="N98" s="20" t="n">
-        <v>9</v>
+        <v>7.3333</v>
       </c>
       <c r="O98" s="20" t="n">
-        <v>8</v>
+        <v>6.1333</v>
       </c>
       <c r="P98" s="20" t="n">
-        <v>7</v>
+        <v>5.9333</v>
       </c>
       <c r="Q98" s="20" t="n">
-        <v>8</v>
+        <v>7.8333</v>
       </c>
       <c r="R98" s="20" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="S98" s="20" t="n">
-        <v>8</v>
+        <v>6.9333</v>
       </c>
       <c r="T98" s="20" t="n">
-        <v>8</v>
+        <v>6.3333</v>
       </c>
       <c r="U98" s="20" t="n">
-        <v>7</v>
+        <v>5.7333</v>
       </c>
       <c r="V98" s="20" t="n">
-        <v>8</v>
+        <v>7.0667</v>
       </c>
       <c r="W98" s="20" t="n">
-        <v>8</v>
+        <v>7.6667</v>
       </c>
     </row>
     <row r="99">
@@ -27713,70 +27713,70 @@
         </is>
       </c>
       <c r="B99" s="18" t="n">
-        <v>156</v>
+        <v>132.0668</v>
       </c>
       <c r="C99" s="19" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="D99" s="20" t="n">
-        <v>8</v>
+        <v>7.2333</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>8</v>
+        <v>6.6667</v>
       </c>
       <c r="F99" s="20" t="n">
-        <v>8</v>
+        <v>7.5667</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>8</v>
+        <v>5.8333</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>9</v>
+        <v>7.8667</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>8</v>
+        <v>6.5667</v>
       </c>
       <c r="L99" s="20" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>8</v>
+        <v>7.6667</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>9</v>
+        <v>8.433299999999999</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>8</v>
+        <v>5.5667</v>
       </c>
       <c r="P99" s="20" t="n">
-        <v>8</v>
+        <v>6.0333</v>
       </c>
       <c r="Q99" s="20" t="n">
-        <v>8</v>
+        <v>7.7667</v>
       </c>
       <c r="R99" s="20" t="n">
-        <v>7</v>
+        <v>6.7333</v>
       </c>
       <c r="S99" s="20" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="T99" s="20" t="n">
-        <v>7</v>
+        <v>4.8667</v>
       </c>
       <c r="U99" s="20" t="n">
-        <v>7</v>
+        <v>5.5667</v>
       </c>
       <c r="V99" s="20" t="n">
-        <v>7</v>
+        <v>6.2667</v>
       </c>
       <c r="W99" s="20" t="n">
-        <v>8</v>
+        <v>7.0333</v>
       </c>
     </row>
     <row r="100">
@@ -27786,70 +27786,70 @@
         </is>
       </c>
       <c r="B100" s="18" t="n">
-        <v>149</v>
+        <v>127.5999</v>
       </c>
       <c r="C100" s="19" t="n">
-        <v>7.45</v>
+        <v>6.38</v>
       </c>
       <c r="D100" s="20" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>8</v>
+        <v>6.3333</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>7</v>
+        <v>6.3667</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>8</v>
+        <v>5.3333</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>8</v>
+        <v>7.3333</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>8</v>
+        <v>7.1333</v>
       </c>
       <c r="P100" s="20" t="n">
-        <v>8</v>
+        <v>6.7667</v>
       </c>
       <c r="Q100" s="20" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="R100" s="20" t="n">
-        <v>7</v>
+        <v>5.3333</v>
       </c>
       <c r="S100" s="20" t="n">
-        <v>8</v>
+        <v>7.1667</v>
       </c>
       <c r="T100" s="20" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="U100" s="20" t="n">
-        <v>7</v>
+        <v>6.2333</v>
       </c>
       <c r="V100" s="20" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W100" s="20" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="101">
@@ -27859,70 +27859,70 @@
         </is>
       </c>
       <c r="B101" s="18" t="n">
-        <v>147</v>
+        <v>124.9667</v>
       </c>
       <c r="C101" s="19" t="n">
-        <v>7.35</v>
+        <v>6.25</v>
       </c>
       <c r="D101" s="20" t="n">
-        <v>8</v>
+        <v>6.5667</v>
       </c>
       <c r="E101" s="20" t="n">
-        <v>8</v>
+        <v>7.3333</v>
       </c>
       <c r="F101" s="20" t="n">
-        <v>8</v>
+        <v>5.5667</v>
       </c>
       <c r="G101" s="20" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="H101" s="20" t="n">
-        <v>7</v>
+        <v>5.8667</v>
       </c>
       <c r="I101" s="20" t="n">
-        <v>6</v>
+        <v>4.9333</v>
       </c>
       <c r="J101" s="20" t="n">
-        <v>8</v>
+        <v>5.9333</v>
       </c>
       <c r="K101" s="20" t="n">
-        <v>8</v>
+        <v>7.7667</v>
       </c>
       <c r="L101" s="20" t="n">
-        <v>8</v>
+        <v>5.4667</v>
       </c>
       <c r="M101" s="20" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="N101" s="20" t="n">
-        <v>7</v>
+        <v>6.2667</v>
       </c>
       <c r="O101" s="20" t="n">
-        <v>8</v>
+        <v>6.2667</v>
       </c>
       <c r="P101" s="20" t="n">
-        <v>8</v>
+        <v>6.9333</v>
       </c>
       <c r="Q101" s="20" t="n">
-        <v>7</v>
+        <v>6.6333</v>
       </c>
       <c r="R101" s="20" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="S101" s="20" t="n">
-        <v>8</v>
+        <v>6.8333</v>
       </c>
       <c r="T101" s="20" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="U101" s="20" t="n">
-        <v>6</v>
+        <v>6.1667</v>
       </c>
       <c r="V101" s="20" t="n">
-        <v>7</v>
+        <v>6.4333</v>
       </c>
       <c r="W101" s="20" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="102">
@@ -27932,70 +27932,70 @@
         </is>
       </c>
       <c r="B102" s="18" t="n">
-        <v>142</v>
+        <v>116.6999</v>
       </c>
       <c r="C102" s="19" t="n">
-        <v>7.1</v>
+        <v>5.83</v>
       </c>
       <c r="D102" s="20" t="n">
-        <v>7</v>
+        <v>6.0667</v>
       </c>
       <c r="E102" s="20" t="n">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="F102" s="20" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="G102" s="20" t="n">
-        <v>7</v>
+        <v>5.8333</v>
       </c>
       <c r="H102" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>6</v>
+        <v>4.8333</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>7</v>
+        <v>5.8333</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="L102" s="20" t="n">
         <v>6</v>
       </c>
       <c r="M102" s="20" t="n">
-        <v>7</v>
+        <v>5.2667</v>
       </c>
       <c r="N102" s="20" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="O102" s="20" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="P102" s="20" t="n">
-        <v>7</v>
+        <v>6.4333</v>
       </c>
       <c r="Q102" s="20" t="n">
-        <v>8</v>
+        <v>7.2333</v>
       </c>
       <c r="R102" s="20" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S102" s="20" t="n">
-        <v>8</v>
+        <v>5.6667</v>
       </c>
       <c r="T102" s="20" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="U102" s="20" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="V102" s="20" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="W102" s="20" t="n">
-        <v>8</v>
+        <v>7.3333</v>
       </c>
     </row>
     <row r="103">
@@ -28005,70 +28005,70 @@
         </is>
       </c>
       <c r="B103" s="18" t="n">
-        <v>132</v>
+        <v>111.9</v>
       </c>
       <c r="C103" s="19" t="n">
-        <v>6.6</v>
+        <v>5.59</v>
       </c>
       <c r="D103" s="20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E103" s="20" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="F103" s="20" t="n">
-        <v>6</v>
+        <v>3.9667</v>
       </c>
       <c r="G103" s="20" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H103" s="20" t="n">
-        <v>6</v>
+        <v>4.9333</v>
       </c>
       <c r="I103" s="20" t="n">
-        <v>6</v>
+        <v>4.8667</v>
       </c>
       <c r="J103" s="20" t="n">
-        <v>7</v>
+        <v>5.6333</v>
       </c>
       <c r="K103" s="20" t="n">
-        <v>8</v>
+        <v>5.5333</v>
       </c>
       <c r="L103" s="20" t="n">
-        <v>8</v>
+        <v>7.1333</v>
       </c>
       <c r="M103" s="20" t="n">
         <v>7</v>
       </c>
       <c r="N103" s="20" t="n">
-        <v>9</v>
+        <v>8.333299999999999</v>
       </c>
       <c r="O103" s="20" t="n">
+        <v>4.7667</v>
+      </c>
+      <c r="P103" s="20" t="n">
+        <v>5.4667</v>
+      </c>
+      <c r="Q103" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="P103" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q103" s="20" t="n">
-        <v>7</v>
-      </c>
       <c r="R103" s="20" t="n">
-        <v>5</v>
+        <v>4.3333</v>
       </c>
       <c r="S103" s="20" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="T103" s="20" t="n">
-        <v>6</v>
+        <v>5.5667</v>
       </c>
       <c r="U103" s="20" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="V103" s="20" t="n">
-        <v>4</v>
+        <v>3.5667</v>
       </c>
       <c r="W103" s="20" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="104">
@@ -28078,70 +28078,70 @@
         </is>
       </c>
       <c r="B104" s="18" t="n">
-        <v>123</v>
+        <v>98.6332</v>
       </c>
       <c r="C104" s="19" t="n">
-        <v>6.15</v>
+        <v>4.93</v>
       </c>
       <c r="D104" s="20" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="E104" s="20" t="n">
-        <v>5</v>
+        <v>4.1333</v>
       </c>
       <c r="F104" s="20" t="n">
-        <v>5</v>
+        <v>4.8333</v>
       </c>
       <c r="G104" s="20" t="n">
-        <v>6</v>
+        <v>4.4333</v>
       </c>
       <c r="H104" s="20" t="n">
-        <v>8</v>
+        <v>6.9333</v>
       </c>
       <c r="I104" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J104" s="20" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="K104" s="20" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="L104" s="20" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="M104" s="20" t="n">
-        <v>7</v>
+        <v>6.7333</v>
       </c>
       <c r="N104" s="20" t="n">
-        <v>8</v>
+        <v>6.7333</v>
       </c>
       <c r="O104" s="20" t="n">
-        <v>6</v>
+        <v>3.3667</v>
       </c>
       <c r="P104" s="20" t="n">
-        <v>6</v>
+        <v>5.6333</v>
       </c>
       <c r="Q104" s="20" t="n">
-        <v>6</v>
+        <v>4.1333</v>
       </c>
       <c r="R104" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S104" s="20" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="T104" s="20" t="n">
-        <v>5</v>
+        <v>4.9667</v>
       </c>
       <c r="U104" s="20" t="n">
-        <v>6</v>
+        <v>5.5667</v>
       </c>
       <c r="V104" s="20" t="n">
-        <v>5</v>
+        <v>4.8667</v>
       </c>
       <c r="W104" s="20" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="105">
@@ -28151,19 +28151,19 @@
         </is>
       </c>
       <c r="B105" s="18" t="n">
-        <v>105</v>
+        <v>79.23319999999998</v>
       </c>
       <c r="C105" s="19" t="n">
-        <v>5.25</v>
+        <v>3.96</v>
       </c>
       <c r="D105" s="20" t="n">
-        <v>4</v>
+        <v>3.5333</v>
       </c>
       <c r="E105" s="20" t="n">
-        <v>3</v>
+        <v>2.0333</v>
       </c>
       <c r="F105" s="20" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="G105" s="20" t="n">
         <v>5</v>
@@ -28178,43 +28178,43 @@
         <v>3</v>
       </c>
       <c r="K105" s="20" t="n">
-        <v>4</v>
+        <v>2.2667</v>
       </c>
       <c r="L105" s="20" t="n">
-        <v>7</v>
+        <v>4.2333</v>
       </c>
       <c r="M105" s="20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N105" s="20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O105" s="20" t="n">
-        <v>4</v>
+        <v>2.9667</v>
       </c>
       <c r="P105" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q105" s="20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R105" s="20" t="n">
-        <v>4</v>
+        <v>3.1333</v>
       </c>
       <c r="S105" s="20" t="n">
-        <v>7</v>
+        <v>6.0333</v>
       </c>
       <c r="T105" s="20" t="n">
-        <v>5</v>
+        <v>3.9667</v>
       </c>
       <c r="U105" s="20" t="n">
-        <v>6</v>
+        <v>3.5333</v>
       </c>
       <c r="V105" s="20" t="n">
-        <v>5</v>
+        <v>4.8333</v>
       </c>
       <c r="W105" s="20" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="106">
@@ -28224,58 +28224,58 @@
         </is>
       </c>
       <c r="B106" s="18" t="n">
-        <v>81</v>
+        <v>62.5667</v>
       </c>
       <c r="C106" s="19" t="n">
-        <v>4.05</v>
+        <v>3.13</v>
       </c>
       <c r="D106" s="20" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="E106" s="20" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="F106" s="20" t="n">
-        <v>3</v>
+        <v>1.7333</v>
       </c>
       <c r="G106" s="20" t="n">
-        <v>5</v>
+        <v>3.3667</v>
       </c>
       <c r="H106" s="20" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="I106" s="20" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J106" s="20" t="n">
         <v>3</v>
       </c>
       <c r="K106" s="20" t="n">
+        <v>1.2667</v>
+      </c>
+      <c r="L106" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M106" s="20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N106" s="20" t="n">
+        <v>4.3667</v>
+      </c>
+      <c r="O106" s="20" t="n">
+        <v>2.7333</v>
+      </c>
+      <c r="P106" s="20" t="n">
+        <v>4.4667</v>
+      </c>
+      <c r="Q106" s="20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R106" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L106" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="M106" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N106" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O106" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="P106" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q106" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R106" s="20" t="n">
-        <v>4</v>
-      </c>
       <c r="S106" s="20" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="T106" s="20" t="n">
         <v>3</v>
@@ -28284,7 +28284,7 @@
         <v>3</v>
       </c>
       <c r="V106" s="20" t="n">
-        <v>6</v>
+        <v>3.2333</v>
       </c>
       <c r="W106" s="20" t="n">
         <v>3</v>
@@ -28297,49 +28297,49 @@
         </is>
       </c>
       <c r="B107" s="18" t="n">
-        <v>62</v>
+        <v>41.0001</v>
       </c>
       <c r="C107" s="19" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="D107" s="20" t="n">
-        <v>3</v>
+        <v>2.1333</v>
       </c>
       <c r="E107" s="20" t="n">
         <v>1</v>
       </c>
       <c r="F107" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G107" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="G107" s="20" t="n">
+      <c r="H107" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="H107" s="20" t="n">
-        <v>4</v>
-      </c>
       <c r="I107" s="20" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J107" s="20" t="n">
-        <v>3</v>
+        <v>1.9667</v>
       </c>
       <c r="K107" s="20" t="n">
         <v>1</v>
       </c>
       <c r="L107" s="20" t="n">
-        <v>4</v>
+        <v>2.8667</v>
       </c>
       <c r="M107" s="20" t="n">
-        <v>3</v>
+        <v>1.5667</v>
       </c>
       <c r="N107" s="20" t="n">
-        <v>4</v>
+        <v>2.9667</v>
       </c>
       <c r="O107" s="20" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="P107" s="20" t="n">
-        <v>4</v>
+        <v>0.4667</v>
       </c>
       <c r="Q107" s="20" t="n">
         <v>2</v>
@@ -28348,19 +28348,19 @@
         <v>2</v>
       </c>
       <c r="S107" s="20" t="n">
-        <v>6</v>
+        <v>4.0333</v>
       </c>
       <c r="T107" s="20" t="n">
-        <v>4</v>
+        <v>2.4333</v>
       </c>
       <c r="U107" s="20" t="n">
         <v>3</v>
       </c>
       <c r="V107" s="20" t="n">
-        <v>3</v>
+        <v>2.6667</v>
       </c>
       <c r="W107" s="20" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="108">
@@ -28370,16 +28370,16 @@
         </is>
       </c>
       <c r="B108" s="18" t="n">
-        <v>44</v>
+        <v>31.2333</v>
       </c>
       <c r="C108" s="19" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="D108" s="20" t="n">
         <v>2</v>
       </c>
       <c r="E108" s="20" t="n">
-        <v>1</v>
+        <v>0.0667</v>
       </c>
       <c r="F108" s="20" t="n">
         <v>1</v>
@@ -28388,34 +28388,34 @@
         <v>2</v>
       </c>
       <c r="H108" s="20" t="n">
-        <v>3</v>
+        <v>1.7333</v>
       </c>
       <c r="I108" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J108" s="20" t="n">
-        <v>3</v>
+        <v>1.6667</v>
       </c>
       <c r="K108" s="20" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="L108" s="20" t="n">
-        <v>3</v>
+        <v>1.6333</v>
       </c>
       <c r="M108" s="20" t="n">
-        <v>3</v>
+        <v>1.7333</v>
       </c>
       <c r="N108" s="20" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="O108" s="20" t="n">
-        <v>1</v>
+        <v>0.7333</v>
       </c>
       <c r="P108" s="20" t="n">
-        <v>2</v>
+        <v>0.8667</v>
       </c>
       <c r="Q108" s="20" t="n">
-        <v>2</v>
+        <v>1.2667</v>
       </c>
       <c r="R108" s="20" t="n">
         <v>2</v>
@@ -28424,16 +28424,16 @@
         <v>4</v>
       </c>
       <c r="T108" s="20" t="n">
+        <v>1.5667</v>
+      </c>
+      <c r="U108" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="U108" s="20" t="n">
-        <v>3</v>
-      </c>
       <c r="V108" s="20" t="n">
-        <v>3</v>
+        <v>1.4333</v>
       </c>
       <c r="W108" s="20" t="n">
-        <v>1</v>
+        <v>1.3333</v>
       </c>
     </row>
     <row r="109">
@@ -28443,67 +28443,67 @@
         </is>
       </c>
       <c r="B109" s="18" t="n">
-        <v>34</v>
+        <v>22.6668</v>
       </c>
       <c r="C109" s="19" t="n">
-        <v>1.7</v>
+        <v>1.13</v>
       </c>
       <c r="D109" s="20" t="n">
-        <v>2</v>
+        <v>1.8667</v>
       </c>
       <c r="E109" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F109" s="20" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="G109" s="20" t="n">
-        <v>2</v>
+        <v>1.3667</v>
       </c>
       <c r="H109" s="20" t="n">
         <v>2</v>
       </c>
       <c r="I109" s="20" t="n">
-        <v>2</v>
+        <v>1.4667</v>
       </c>
       <c r="J109" s="20" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K109" s="20" t="n">
         <v>1</v>
       </c>
       <c r="L109" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M109" s="20" t="n">
-        <v>2</v>
+        <v>0.2667</v>
       </c>
       <c r="N109" s="20" t="n">
         <v>1</v>
       </c>
       <c r="O109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="P109" s="20" t="n">
-        <v>2</v>
-      </c>
       <c r="Q109" s="20" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="R109" s="20" t="n">
         <v>2</v>
       </c>
       <c r="S109" s="20" t="n">
-        <v>4</v>
+        <v>3.1333</v>
       </c>
       <c r="T109" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U109" s="20" t="n">
         <v>2</v>
       </c>
       <c r="V109" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W109" s="20" t="n">
         <v>2</v>
@@ -28516,28 +28516,28 @@
         </is>
       </c>
       <c r="B110" s="18" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="C110" s="19" t="n">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="D110" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="20" t="n">
-        <v>1</v>
+        <v>0.3667</v>
       </c>
       <c r="H110" s="20" t="n">
         <v>2</v>
       </c>
       <c r="I110" s="20" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J110" s="20" t="n">
         <v>0</v>
@@ -28546,7 +28546,7 @@
         <v>1</v>
       </c>
       <c r="L110" s="20" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M110" s="20" t="n">
         <v>0</v>
@@ -28564,16 +28564,16 @@
         <v>0</v>
       </c>
       <c r="R110" s="20" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="S110" s="20" t="n">
         <v>3</v>
       </c>
       <c r="T110" s="20" t="n">
-        <v>1</v>
+        <v>1.3333</v>
       </c>
       <c r="U110" s="20" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="V110" s="20" t="n">
         <v>0</v>
@@ -28589,13 +28589,13 @@
         </is>
       </c>
       <c r="B111" s="18" t="n">
-        <v>16</v>
+        <v>0.4665</v>
       </c>
       <c r="C111" s="19" t="n">
-        <v>0.8</v>
+        <v>0.02</v>
       </c>
       <c r="D111" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="E111" s="20" t="n">
         <v>0</v>
@@ -28607,52 +28607,52 @@
         <v>0</v>
       </c>
       <c r="H111" s="20" t="n">
-        <v>2</v>
+        <v>0.0667</v>
       </c>
       <c r="I111" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" s="20" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="L111" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" s="20" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="O111" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="Q111" s="20" t="n">
         <v>0</v>
       </c>
       <c r="R111" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="S111" s="20" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="T111" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="U111" s="20" t="n">
-        <v>1</v>
+        <v>0.0333</v>
       </c>
       <c r="V111" s="20" t="n">
         <v>0</v>
       </c>
       <c r="W111" s="20" t="n">
-        <v>2</v>
+        <v>0.0667</v>
       </c>
     </row>
   </sheetData>
